--- a/AAII_Financials/Quarterly/BRTX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BRTX_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="92">
   <si>
     <t>BRTX</t>
   </si>
@@ -1904,8 +1904,8 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>100</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>4</v>

--- a/AAII_Financials/Quarterly/BRTX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BRTX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
   <si>
     <t>BRTX</t>
   </si>
@@ -656,140 +656,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -797,26 +804,26 @@
         <v>4</v>
       </c>
       <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
         <v>100</v>
       </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
       <c r="H8" s="3">
         <v>0</v>
       </c>
       <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3">
         <v>100</v>
       </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
       <c r="L8" s="3">
         <v>0</v>
       </c>
@@ -880,8 +887,14 @@
       <c r="AF8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -966,14 +979,20 @@
       <c r="AD9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE9" s="3">
-        <v>0</v>
+      <c r="AE9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1058,14 +1077,20 @@
       <c r="AD10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE10" s="3">
-        <v>0</v>
+      <c r="AE10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,37 +1123,39 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E12" s="3">
+        <v>700</v>
+      </c>
+      <c r="F12" s="3">
         <v>900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>1000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>1500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>1000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>1100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>800</v>
-      </c>
-      <c r="K12" s="3">
-        <v>200</v>
-      </c>
-      <c r="L12" s="3">
-        <v>200</v>
       </c>
       <c r="M12" s="3">
         <v>200</v>
@@ -1140,31 +1167,31 @@
         <v>200</v>
       </c>
       <c r="P12" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>200</v>
+      </c>
+      <c r="R12" s="3">
         <v>300</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>400</v>
-      </c>
-      <c r="R12" s="3">
-        <v>200</v>
       </c>
       <c r="S12" s="3">
         <v>400</v>
       </c>
       <c r="T12" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="U12" s="3">
         <v>400</v>
       </c>
       <c r="V12" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="W12" s="3">
         <v>400</v>
       </c>
       <c r="X12" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="Y12" s="3">
         <v>400</v>
@@ -1173,25 +1200,31 @@
         <v>400</v>
       </c>
       <c r="AA12" s="3">
+        <v>400</v>
+      </c>
+      <c r="AB12" s="3">
+        <v>400</v>
+      </c>
+      <c r="AC12" s="3">
         <v>200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,13 +1315,19 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -1306,56 +1345,56 @@
         <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>-300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>16200</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>4700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>-100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>3200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>-400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>1300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>1000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>300</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
@@ -1366,16 +1405,22 @@
         <v>0</v>
       </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>100</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1511,14 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,100 +1548,108 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3100</v>
+        <v>4100</v>
       </c>
       <c r="E17" s="3">
         <v>3200</v>
       </c>
       <c r="F17" s="3">
+        <v>3100</v>
+      </c>
+      <c r="G17" s="3">
+        <v>3200</v>
+      </c>
+      <c r="H17" s="3">
         <v>5800</v>
-      </c>
-      <c r="G17" s="3">
-        <v>4700</v>
-      </c>
-      <c r="H17" s="3">
-        <v>4600</v>
       </c>
       <c r="I17" s="3">
         <v>4700</v>
       </c>
       <c r="J17" s="3">
+        <v>4600</v>
+      </c>
+      <c r="K17" s="3">
+        <v>4700</v>
+      </c>
+      <c r="L17" s="3">
         <v>4800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>20200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>3700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>3600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>15100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>5600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>4100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>3100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>2700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>2800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>3200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>2100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>2300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>1600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>1800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>2600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>2600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>1900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1598,91 +1657,97 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-3100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="H18" s="3">
         <v>-5800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-4700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-4600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-4600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-4800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-20200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-3700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-3600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-15100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-5600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-1200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-4100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-1800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-3100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-2700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-2800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-3200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,8 +1780,10 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1724,20 +1791,20 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>400</v>
+      </c>
+      <c r="F20" s="3">
+        <v>200</v>
+      </c>
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>300</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
@@ -1760,44 +1827,44 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-2100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-2100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>1100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>200</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
@@ -1807,8 +1874,14 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1816,91 +1889,97 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-2900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="H21" s="3">
         <v>-5600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-4300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-4600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-4600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-4800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-20200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-3700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-3500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-15000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-5500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-3200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-6200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-3100</v>
-      </c>
-      <c r="U21" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="V21" s="3">
-        <v>-2800</v>
       </c>
       <c r="W21" s="3">
         <v>-2800</v>
       </c>
       <c r="X21" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-1800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1916,175 +1995,187 @@
       <c r="G22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
+      <c r="H22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
       </c>
       <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
         <v>200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>200</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
         <v>1400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>1400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>1900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>1300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>1100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>1300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>300</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>200</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>200</v>
       </c>
       <c r="AE22" s="3">
         <v>200</v>
       </c>
       <c r="AF22" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH22" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="F23" s="3">
         <v>-2900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-3000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-5700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-4300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-4700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-4700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-4800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-20400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-4200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-4100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-15700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-5800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-4700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-7600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-1600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-5100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-4200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-3900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-3600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2175,8 +2266,14 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2364,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="F26" s="3">
         <v>-2900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-3000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-5700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-4300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-4700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-4700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-4800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-20400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-4200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-4100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-15700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-5800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-4700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-7600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-1600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-5100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-4200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-3900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-3600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="F27" s="3">
         <v>-2900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-3000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-5700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-4300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-4700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-4700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-4800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-20400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-4200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-4100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-15700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-5800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-4700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-7600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-1600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-5100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-4200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-3900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-3600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2658,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2756,14 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2854,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,8 +2952,14 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2828,20 +2967,20 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-300</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
@@ -2864,44 +3003,44 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>2100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>2100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-1100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-200</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
@@ -2911,100 +3050,112 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="F33" s="3">
         <v>-2900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-3000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-5700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-4300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-4700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-4700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-4800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-20400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-4200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-4100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-15700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-5800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-4700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-7600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-1600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-5100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-4200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-3900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-3600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3246,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="F35" s="3">
         <v>-2900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-3000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-5700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-4300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-4700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-4700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-4800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-20400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-4200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-4100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-15700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-5800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-4700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-7600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-1600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-5100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-4200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-3900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-3600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3487,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,89 +3523,91 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>900</v>
+      </c>
+      <c r="F41" s="3">
         <v>2400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>6600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>17900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>19300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>21000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>2500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>3100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>300</v>
       </c>
-      <c r="R41" s="3">
-        <v>0</v>
-      </c>
-      <c r="S41" s="3">
-        <v>0</v>
-      </c>
       <c r="T41" s="3">
+        <v>0</v>
+      </c>
+      <c r="U41" s="3">
+        <v>0</v>
+      </c>
+      <c r="V41" s="3">
         <v>100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>100</v>
       </c>
-      <c r="Y41" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z41" s="3">
-        <v>0</v>
-      </c>
       <c r="AA41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="3">
         <v>500</v>
       </c>
-      <c r="AB41" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC41" s="3">
-        <v>0</v>
-      </c>
       <c r="AD41" s="3">
         <v>0</v>
       </c>
@@ -3444,32 +3617,38 @@
       <c r="AF41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E42" s="3">
+        <v>10200</v>
+      </c>
+      <c r="F42" s="3">
         <v>9800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>9800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>10500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>13100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>9900</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3482,11 +3661,11 @@
       <c r="N42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3">
-        <v>0</v>
+      <c r="O42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
@@ -3536,8 +3715,14 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3628,8 +3813,14 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,8 +3911,14 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3729,10 +3926,10 @@
         <v>300</v>
       </c>
       <c r="E45" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F45" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G45" s="3">
         <v>400</v>
@@ -3744,28 +3941,28 @@
         <v>400</v>
       </c>
       <c r="J45" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K45" s="3">
         <v>400</v>
       </c>
       <c r="L45" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="M45" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="N45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O45" s="3">
         <v>100</v>
       </c>
       <c r="P45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
@@ -3774,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="T45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U45" s="3">
         <v>0</v>
@@ -3792,7 +3989,7 @@
         <v>0</v>
       </c>
       <c r="Z45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA45" s="3">
         <v>0</v>
@@ -3812,100 +4009,112 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>11400</v>
+      </c>
+      <c r="F46" s="3">
         <v>12600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>12000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>12800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>15100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>16900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>18300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>19900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>21500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>2600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>3200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>1400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>100</v>
       </c>
-      <c r="Z46" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="3">
         <v>500</v>
       </c>
-      <c r="AB46" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC46" s="3">
-        <v>0</v>
-      </c>
       <c r="AD46" s="3">
         <v>0</v>
       </c>
       <c r="AE46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG46" s="3">
         <v>100</v>
       </c>
-      <c r="AF46" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3996,8 +4205,14 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4017,79 +4232,85 @@
         <v>500</v>
       </c>
       <c r="I48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="J48" s="3">
         <v>500</v>
       </c>
       <c r="K48" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="L48" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="M48" s="3">
         <v>400</v>
       </c>
       <c r="N48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="O48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="P48" s="3">
         <v>500</v>
       </c>
       <c r="Q48" s="3">
+        <v>500</v>
+      </c>
+      <c r="R48" s="3">
+        <v>500</v>
+      </c>
+      <c r="S48" s="3">
         <v>600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>700</v>
-      </c>
-      <c r="T48" s="3">
-        <v>100</v>
-      </c>
-      <c r="U48" s="3">
-        <v>100</v>
       </c>
       <c r="V48" s="3">
         <v>100</v>
       </c>
       <c r="W48" s="3">
+        <v>100</v>
+      </c>
+      <c r="X48" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y48" s="3">
         <v>200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>200</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>300</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>300</v>
       </c>
       <c r="AA48" s="3">
         <v>300</v>
       </c>
       <c r="AB48" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC48" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD48" s="3">
         <v>400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4097,22 +4318,22 @@
         <v>700</v>
       </c>
       <c r="E49" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="F49" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="G49" s="3">
         <v>800</v>
       </c>
       <c r="H49" s="3">
+        <v>800</v>
+      </c>
+      <c r="I49" s="3">
+        <v>800</v>
+      </c>
+      <c r="J49" s="3">
         <v>500</v>
-      </c>
-      <c r="I49" s="3">
-        <v>600</v>
-      </c>
-      <c r="J49" s="3">
-        <v>600</v>
       </c>
       <c r="K49" s="3">
         <v>600</v>
@@ -4127,10 +4348,10 @@
         <v>600</v>
       </c>
       <c r="O49" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="P49" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="Q49" s="3">
         <v>700</v>
@@ -4142,10 +4363,10 @@
         <v>700</v>
       </c>
       <c r="T49" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="U49" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="V49" s="3">
         <v>800</v>
@@ -4157,10 +4378,10 @@
         <v>800</v>
       </c>
       <c r="Y49" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="Z49" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="AA49" s="3">
         <v>900</v>
@@ -4175,13 +4396,19 @@
         <v>900</v>
       </c>
       <c r="AE49" s="3">
+        <v>900</v>
+      </c>
+      <c r="AF49" s="3">
+        <v>900</v>
+      </c>
+      <c r="AG49" s="3">
         <v>1000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4499,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,31 +4597,37 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
         <v>0</v>
       </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="E52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -4418,17 +4657,17 @@
         <v>0</v>
       </c>
       <c r="T52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3">
         <v>400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>200</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
-      </c>
-      <c r="W52" s="3">
-        <v>0</v>
-      </c>
       <c r="X52" s="3">
         <v>0</v>
       </c>
@@ -4442,22 +4681,28 @@
         <v>0</v>
       </c>
       <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="3">
         <v>100</v>
       </c>
-      <c r="AC52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD52" s="3">
-        <v>0</v>
-      </c>
       <c r="AE52" s="3">
         <v>0</v>
       </c>
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4793,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>12600</v>
+      </c>
+      <c r="F54" s="3">
         <v>13800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>13300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>14100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>16400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>17900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>19400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>20900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>22500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>2200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>2900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>3700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>4300</v>
-      </c>
-      <c r="P54" s="3">
-        <v>1400</v>
-      </c>
-      <c r="Q54" s="3">
-        <v>1600</v>
       </c>
       <c r="R54" s="3">
         <v>1400</v>
       </c>
       <c r="S54" s="3">
+        <v>1600</v>
+      </c>
+      <c r="T54" s="3">
+        <v>1400</v>
+      </c>
+      <c r="U54" s="3">
         <v>1500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>2400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1600</v>
-      </c>
-      <c r="W54" s="3">
-        <v>1200</v>
-      </c>
-      <c r="X54" s="3">
-        <v>1300</v>
       </c>
       <c r="Y54" s="3">
         <v>1200</v>
       </c>
       <c r="Z54" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AA54" s="3">
         <v>1200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AC54" s="3">
         <v>1800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>1400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>1400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>1500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>1600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4931,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,8 +4967,10 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4717,99 +4978,105 @@
         <v>200</v>
       </c>
       <c r="E57" s="3">
+        <v>200</v>
+      </c>
+      <c r="F57" s="3">
+        <v>200</v>
+      </c>
+      <c r="G57" s="3">
         <v>300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>200</v>
-      </c>
-      <c r="K57" s="3">
-        <v>100</v>
-      </c>
-      <c r="L57" s="3">
-        <v>100</v>
       </c>
       <c r="M57" s="3">
         <v>100</v>
       </c>
       <c r="N57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O57" s="3">
         <v>100</v>
       </c>
       <c r="P57" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q57" s="3">
         <v>100</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
+        <v>100</v>
+      </c>
+      <c r="S57" s="3">
+        <v>0</v>
+      </c>
+      <c r="T57" s="3">
         <v>2000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>2000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>1700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>1500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>1600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>1900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>2100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>2300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>2400</v>
-      </c>
-      <c r="AA57" s="3">
-        <v>2500</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>2700</v>
       </c>
       <c r="AC57" s="3">
         <v>2500</v>
       </c>
       <c r="AD57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AE57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="AF57" s="3">
         <v>2300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>2300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>4</v>
+      <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
@@ -4827,14 +5094,14 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>100</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -4842,242 +5109,260 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>1100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>8000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>7100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>7500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>5500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>3500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>3600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>3200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>4400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>3700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>3500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>2900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>2400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>1900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>1900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>900</v>
+      </c>
+      <c r="F59" s="3">
         <v>700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>8300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>4600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>4400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>4100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>3600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>3700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>3700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>3900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>2700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>2400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>2500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>2100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>1800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>1700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F60" s="3">
         <v>900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>18400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>13700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>13700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>11100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>8700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>9300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>8900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>10600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>8800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>8400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>8000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>7000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>6100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>5800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5103,26 +5388,26 @@
         <v>0</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>5800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>5000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>4700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>4300</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -5130,118 +5415,124 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>1200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>400</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA61" s="3">
-        <v>200</v>
       </c>
       <c r="AB61" s="3">
         <v>100</v>
       </c>
       <c r="AC61" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AD61" s="3">
         <v>100</v>
       </c>
       <c r="AE61" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF61" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG61" s="3">
         <v>300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3">
         <v>100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>100</v>
-      </c>
-      <c r="G62" s="3">
-        <v>200</v>
-      </c>
-      <c r="H62" s="3">
-        <v>200</v>
       </c>
       <c r="I62" s="3">
         <v>200</v>
       </c>
       <c r="J62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L62" s="3">
         <v>300</v>
       </c>
       <c r="M62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="N62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="O62" s="3">
         <v>400</v>
       </c>
       <c r="P62" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>400</v>
+      </c>
+      <c r="R62" s="3">
         <v>15100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>15200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>500</v>
       </c>
-      <c r="T62" s="3">
-        <v>0</v>
-      </c>
-      <c r="U62" s="3">
-        <v>0</v>
-      </c>
       <c r="V62" s="3">
         <v>0</v>
       </c>
       <c r="W62" s="3">
+        <v>0</v>
+      </c>
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="3">
         <v>100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>100</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>0</v>
-      </c>
       <c r="AA62" s="3">
         <v>0</v>
       </c>
@@ -5255,13 +5546,19 @@
         <v>0</v>
       </c>
       <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="3">
         <v>400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5649,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5747,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5845,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F66" s="3">
         <v>1000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>900</v>
-      </c>
-      <c r="I66" s="3">
-        <v>900</v>
-      </c>
-      <c r="J66" s="3">
-        <v>800</v>
       </c>
       <c r="K66" s="3">
         <v>900</v>
       </c>
       <c r="L66" s="3">
+        <v>800</v>
+      </c>
+      <c r="M66" s="3">
+        <v>900</v>
+      </c>
+      <c r="N66" s="3">
         <v>7100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>6700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>6400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>5700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>16500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>16100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>18900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>14200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>13900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>11400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>9200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>9800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>10200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>11100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>8900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>8600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>8100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>7100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>6200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>6600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5983,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +6077,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6175,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6273,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6371,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-148900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-167100</v>
+      </c>
+      <c r="F72" s="3">
         <v>-164200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-161300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-158300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-152600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-148300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-143600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-139000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-134100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-113700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-109600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-105500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-89800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-84100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-83200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-86100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-78600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-77000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-72000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-67800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-63900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-60400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-57400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-53900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-51400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-49500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-47500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-44700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-42000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-39900</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6567,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6665,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6763,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>11500</v>
+      </c>
+      <c r="F76" s="3">
         <v>12800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>12400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>13500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>15800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>17000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>18600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>20100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>21600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-4900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-3800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-2700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-1300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-15100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>-14400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>-17500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>-12800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>-12400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>-8900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>-7700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>-8600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>-8900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>-9900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>-6800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>-6700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>-5700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>-4700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6959,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="F81" s="3">
         <v>-2900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-3000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-5700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-4300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-4700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-4700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-4800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-20400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-4200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-4100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-15700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-5800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-4700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-7600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-1600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-5100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-4200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-3900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-3600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7200,10 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6850,7 +7247,7 @@
         <v>0</v>
       </c>
       <c r="Q83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -6859,7 +7256,7 @@
         <v>100</v>
       </c>
       <c r="T83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U83" s="3">
         <v>100</v>
@@ -6897,8 +7294,14 @@
       <c r="AF83" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7392,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7490,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7588,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7686,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7784,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-2300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-1600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-1600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-1800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-1700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-1400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-2000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-1600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-800</v>
-      </c>
-      <c r="AD89" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="AE89" s="3">
-        <v>-1100</v>
       </c>
       <c r="AF89" s="3">
         <v>-1200</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AH89" s="3">
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,52 +7922,54 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
       </c>
       <c r="K91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>4</v>
+        <v>-100</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="P91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -7539,23 +7980,23 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z91" s="3" t="s">
-        <v>4</v>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>4</v>
@@ -7569,14 +8010,20 @@
       <c r="AD91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +8114,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,38 +8212,44 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-4900</v>
       </c>
       <c r="E94" s="3">
+        <v>100</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>2500</v>
       </c>
-      <c r="G94" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="J94" s="3">
         <v>-9900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>4</v>
       </c>
@@ -7800,11 +8259,11 @@
       <c r="O94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="P94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
@@ -7815,29 +8274,29 @@
       <c r="T94" s="3">
         <v>0</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB94" s="3">
-        <v>0</v>
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC94" s="3">
         <v>0</v>
@@ -7851,8 +8310,14 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8350,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8444,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8542,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8640,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,23 +8738,29 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>100</v>
+      </c>
+      <c r="F100" s="3">
         <v>1900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>400</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
@@ -8280,73 +8771,79 @@
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>21100</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>3500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>1200</v>
-      </c>
-      <c r="R100" s="3">
-        <v>500</v>
-      </c>
-      <c r="S100" s="3">
-        <v>1700</v>
       </c>
       <c r="T100" s="3">
         <v>500</v>
       </c>
       <c r="U100" s="3">
+        <v>1700</v>
+      </c>
+      <c r="V100" s="3">
+        <v>500</v>
+      </c>
+      <c r="W100" s="3">
         <v>2200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>2400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>1600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>1500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>1000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>1800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>1200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>1100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,89 +8934,95 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F102" s="3">
         <v>700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-4900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-11400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-1400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>19900</v>
-      </c>
-      <c r="L102" s="3">
-        <v>-600</v>
-      </c>
-      <c r="M102" s="3">
-        <v>-700</v>
       </c>
       <c r="N102" s="3">
         <v>-600</v>
       </c>
       <c r="O102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="P102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Q102" s="3">
         <v>2900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>300</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
         <v>-100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-1200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>400</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
         <v>100</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>500</v>
       </c>
-      <c r="AB102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC102" s="3">
-        <v>0</v>
-      </c>
       <c r="AD102" s="3">
         <v>0</v>
       </c>
@@ -8527,6 +9030,12 @@
         <v>0</v>
       </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>-500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BRTX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BRTX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
   <si>
     <t>BRTX</t>
   </si>
@@ -656,152 +656,156 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>4</v>
+      <c r="D8" s="3">
+        <v>100</v>
       </c>
       <c r="E8" s="3">
         <v>0</v>
@@ -810,11 +814,11 @@
         <v>0</v>
       </c>
       <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
         <v>100</v>
       </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
       <c r="I8" s="3">
         <v>0</v>
       </c>
@@ -822,11 +826,11 @@
         <v>0</v>
       </c>
       <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
         <v>100</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
       <c r="M8" s="3">
         <v>0</v>
       </c>
@@ -893,13 +897,16 @@
       <c r="AH8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>4</v>
+      <c r="D9" s="3">
+        <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>4</v>
@@ -985,19 +992,22 @@
       <c r="AF9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG9" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>4</v>
+      <c r="D10" s="3">
+        <v>100</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>4</v>
@@ -1083,14 +1093,17 @@
       <c r="AF10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH10" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,40 +1138,41 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E12" s="3">
         <v>1100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
+        <v>900</v>
+      </c>
+      <c r="I12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J12" s="3">
+        <v>700</v>
+      </c>
+      <c r="K12" s="3">
         <v>1000</v>
       </c>
-      <c r="H12" s="3">
-        <v>1500</v>
-      </c>
-      <c r="I12" s="3">
-        <v>700</v>
-      </c>
-      <c r="J12" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>800</v>
-      </c>
-      <c r="M12" s="3">
-        <v>200</v>
       </c>
       <c r="N12" s="3">
         <v>200</v>
@@ -1173,16 +1187,16 @@
         <v>200</v>
       </c>
       <c r="R12" s="3">
+        <v>200</v>
+      </c>
+      <c r="S12" s="3">
         <v>300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>200</v>
-      </c>
-      <c r="U12" s="3">
-        <v>400</v>
       </c>
       <c r="V12" s="3">
         <v>400</v>
@@ -1191,10 +1205,10 @@
         <v>400</v>
       </c>
       <c r="X12" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y12" s="3">
         <v>500</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>400</v>
       </c>
       <c r="Z12" s="3">
         <v>400</v>
@@ -1206,25 +1220,28 @@
         <v>400</v>
       </c>
       <c r="AC12" s="3">
+        <v>400</v>
+      </c>
+      <c r="AD12" s="3">
         <v>200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>600</v>
-      </c>
-      <c r="AF12" s="3">
-        <v>800</v>
       </c>
       <c r="AG12" s="3">
         <v>800</v>
       </c>
       <c r="AH12" s="3">
+        <v>800</v>
+      </c>
+      <c r="AI12" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,19 +1338,22 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
@@ -1351,14 +1371,14 @@
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>-300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>16200</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
@@ -1366,38 +1386,38 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>4700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>3200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>300</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
@@ -1411,16 +1431,19 @@
         <v>0</v>
       </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>100</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E17" s="3">
         <v>4100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>20200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>15100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1800</v>
-      </c>
-      <c r="AE17" s="3">
-        <v>2600</v>
       </c>
       <c r="AF17" s="3">
         <v>2600</v>
       </c>
       <c r="AG17" s="3">
+        <v>2600</v>
+      </c>
+      <c r="AH17" s="3">
         <v>1900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>-2500</v>
       </c>
       <c r="E18" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-3200</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-3100</v>
       </c>
       <c r="G18" s="3">
         <v>-3100</v>
       </c>
       <c r="H18" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="I18" s="3">
         <v>-5800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-4700</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-4600</v>
       </c>
       <c r="K18" s="3">
         <v>-4600</v>
       </c>
       <c r="L18" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="M18" s="3">
         <v>-4800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-20200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-15100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-4100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1800</v>
-      </c>
-      <c r="AE18" s="3">
-        <v>-2600</v>
       </c>
       <c r="AF18" s="3">
         <v>-2600</v>
       </c>
       <c r="AG18" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="AH18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,32 +1815,33 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>-1600</v>
       </c>
       <c r="E20" s="3">
-        <v>400</v>
+        <v>1900</v>
       </c>
       <c r="F20" s="3">
+        <v>4400</v>
+      </c>
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
-        <v>100</v>
-      </c>
       <c r="H20" s="3">
-        <v>100</v>
+        <v>-2600</v>
       </c>
       <c r="I20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
@@ -1833,40 +1867,40 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
-        <v>-2100</v>
+        <v>0</v>
       </c>
       <c r="T20" s="3">
         <v>-2100</v>
       </c>
       <c r="U20" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="V20" s="3">
         <v>1100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-100</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>200</v>
       </c>
       <c r="AC20" s="3">
         <v>200</v>
       </c>
       <c r="AD20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AE20" s="3">
         <v>0</v>
@@ -1880,70 +1914,73 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>-4000</v>
       </c>
       <c r="E21" s="3">
-        <v>-2800</v>
+        <v>-2200</v>
       </c>
       <c r="F21" s="3">
-        <v>-2900</v>
+        <v>1200</v>
       </c>
       <c r="G21" s="3">
         <v>-2900</v>
       </c>
       <c r="H21" s="3">
-        <v>-5600</v>
+        <v>-5700</v>
       </c>
       <c r="I21" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="J21" s="3">
         <v>-4300</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-4600</v>
       </c>
       <c r="K21" s="3">
         <v>-4600</v>
       </c>
       <c r="L21" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="M21" s="3">
         <v>-4800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-20200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-3700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-3500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-5500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-3200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-6200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-3100</v>
-      </c>
-      <c r="W21" s="3">
-        <v>-2800</v>
       </c>
       <c r="X21" s="3">
         <v>-2800</v>
@@ -1952,34 +1989,37 @@
         <v>-2800</v>
       </c>
       <c r="Z21" s="3">
-        <v>-2100</v>
+        <v>-2800</v>
       </c>
       <c r="AA21" s="3">
         <v>-2100</v>
       </c>
       <c r="AB21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="AC21" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-1700</v>
-      </c>
-      <c r="AE21" s="3">
-        <v>-2500</v>
       </c>
       <c r="AF21" s="3">
         <v>-2500</v>
       </c>
       <c r="AG21" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="AH21" s="3">
         <v>-1800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2001,8 +2041,8 @@
       <c r="I22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2011,61 +2051,61 @@
         <v>0</v>
       </c>
       <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
         <v>200</v>
-      </c>
-      <c r="N22" s="3">
-        <v>500</v>
       </c>
       <c r="O22" s="3">
         <v>500</v>
       </c>
       <c r="P22" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q22" s="3">
         <v>600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>200</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
       <c r="S22" s="3">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="T22" s="3">
         <v>1400</v>
       </c>
       <c r="U22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="V22" s="3">
         <v>900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1300</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>400</v>
       </c>
       <c r="AC22" s="3">
         <v>400</v>
       </c>
       <c r="AD22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AE22" s="3">
         <v>300</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>200</v>
       </c>
       <c r="AF22" s="3">
         <v>200</v>
@@ -2074,108 +2114,114 @@
         <v>200</v>
       </c>
       <c r="AH22" s="3">
+        <v>200</v>
+      </c>
+      <c r="AI22" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>4</v>
+      <c r="D23" s="3">
+        <v>-4000</v>
       </c>
       <c r="E23" s="3">
-        <v>-2800</v>
+        <v>-2200</v>
       </c>
       <c r="F23" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G23" s="3">
         <v>-2900</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-3000</v>
       </c>
       <c r="H23" s="3">
         <v>-5700</v>
       </c>
       <c r="I23" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="J23" s="3">
         <v>-4300</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-4700</v>
       </c>
       <c r="K23" s="3">
         <v>-4700</v>
       </c>
       <c r="L23" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="M23" s="3">
         <v>-4800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-20400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-15700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-5800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-4700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-7600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-5100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-4200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-2700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-2100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2272,8 +2318,11 @@
       <c r="AH24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>4</v>
+      <c r="D26" s="3">
+        <v>-4000</v>
       </c>
       <c r="E26" s="3">
-        <v>-2800</v>
+        <v>-2200</v>
       </c>
       <c r="F26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G26" s="3">
         <v>-2900</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-3000</v>
       </c>
       <c r="H26" s="3">
         <v>-5700</v>
       </c>
       <c r="I26" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="J26" s="3">
         <v>-4300</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-4700</v>
       </c>
       <c r="K26" s="3">
         <v>-4700</v>
       </c>
       <c r="L26" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="M26" s="3">
         <v>-4800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-20400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-15700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-5800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-7600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-5100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-4200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-2700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-2100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>4</v>
+      <c r="D27" s="3">
+        <v>-4000</v>
       </c>
       <c r="E27" s="3">
-        <v>-2800</v>
+        <v>-2200</v>
       </c>
       <c r="F27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G27" s="3">
         <v>-2900</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-3000</v>
       </c>
       <c r="H27" s="3">
         <v>-5700</v>
       </c>
       <c r="I27" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="J27" s="3">
         <v>-4300</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-4700</v>
       </c>
       <c r="K27" s="3">
         <v>-4700</v>
       </c>
       <c r="L27" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="M27" s="3">
         <v>-4800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-20400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-15700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-5800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-7600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-5100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-4200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-2700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-2100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,32 +3025,35 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>1600</v>
       </c>
       <c r="E32" s="3">
-        <v>-400</v>
+        <v>-1900</v>
       </c>
       <c r="F32" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
-        <v>-100</v>
-      </c>
       <c r="H32" s="3">
-        <v>-100</v>
+        <v>2600</v>
       </c>
       <c r="I32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
@@ -3009,40 +3079,40 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="T32" s="3">
         <v>2100</v>
       </c>
       <c r="U32" s="3">
+        <v>2100</v>
+      </c>
+      <c r="V32" s="3">
         <v>-1100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>100</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-200</v>
       </c>
       <c r="AC32" s="3">
         <v>-200</v>
       </c>
       <c r="AD32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="AE32" s="3">
         <v>0</v>
@@ -3056,106 +3126,112 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>4</v>
+      <c r="D33" s="3">
+        <v>-4000</v>
       </c>
       <c r="E33" s="3">
-        <v>-2800</v>
+        <v>-2200</v>
       </c>
       <c r="F33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G33" s="3">
         <v>-2900</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-3000</v>
       </c>
       <c r="H33" s="3">
         <v>-5700</v>
       </c>
       <c r="I33" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="J33" s="3">
         <v>-4300</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-4700</v>
       </c>
       <c r="K33" s="3">
         <v>-4700</v>
       </c>
       <c r="L33" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="M33" s="3">
         <v>-4800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-20400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-15700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-5800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-7600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-5100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-4200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-2700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-2100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>4</v>
+      <c r="D35" s="3">
+        <v>-4000</v>
       </c>
       <c r="E35" s="3">
-        <v>-2800</v>
+        <v>-2200</v>
       </c>
       <c r="F35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G35" s="3">
         <v>-2900</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-3000</v>
       </c>
       <c r="H35" s="3">
         <v>-5700</v>
       </c>
       <c r="I35" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="J35" s="3">
         <v>-4300</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-4700</v>
       </c>
       <c r="K35" s="3">
         <v>-4700</v>
       </c>
       <c r="L35" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="M35" s="3">
         <v>-4800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-20400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-15700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-5800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-7600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-5100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-4200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-2700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-2100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,92 +3611,93 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E41" s="3">
         <v>1200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2400</v>
-      </c>
-      <c r="G41" s="3">
-        <v>1800</v>
       </c>
       <c r="H41" s="3">
         <v>1800</v>
       </c>
       <c r="I41" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J41" s="3">
         <v>1700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>17900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>19300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>21000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>300</v>
       </c>
-      <c r="T41" s="3">
-        <v>0</v>
-      </c>
       <c r="U41" s="3">
         <v>0</v>
       </c>
       <c r="V41" s="3">
+        <v>0</v>
+      </c>
+      <c r="W41" s="3">
         <v>100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>500</v>
-      </c>
-      <c r="Y41" s="3">
-        <v>100</v>
       </c>
       <c r="Z41" s="3">
         <v>100</v>
       </c>
       <c r="AA41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB41" s="3">
         <v>0</v>
       </c>
       <c r="AC41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="3">
         <v>500</v>
       </c>
-      <c r="AD41" s="3">
-        <v>0</v>
-      </c>
       <c r="AE41" s="3">
         <v>0</v>
       </c>
@@ -3623,35 +3710,38 @@
       <c r="AH41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E42" s="3">
         <v>15300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>10200</v>
-      </c>
-      <c r="F42" s="3">
-        <v>9800</v>
       </c>
       <c r="G42" s="3">
         <v>9800</v>
       </c>
       <c r="H42" s="3">
+        <v>9800</v>
+      </c>
+      <c r="I42" s="3">
         <v>10500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>13100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>9900</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3667,8 +3757,8 @@
       <c r="P42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -3721,8 +3811,11 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3819,8 +3912,11 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3917,8 +4013,11 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3932,7 +4031,7 @@
         <v>300</v>
       </c>
       <c r="G45" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H45" s="3">
         <v>400</v>
@@ -3947,16 +4046,16 @@
         <v>400</v>
       </c>
       <c r="L45" s="3">
+        <v>400</v>
+      </c>
+      <c r="M45" s="3">
         <v>500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="N45" s="3">
-        <v>0</v>
-      </c>
       <c r="O45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P45" s="3">
         <v>100</v>
@@ -3965,7 +4064,7 @@
         <v>100</v>
       </c>
       <c r="R45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S45" s="3">
         <v>0</v>
@@ -3977,23 +4076,23 @@
         <v>0</v>
       </c>
       <c r="V45" s="3">
+        <v>0</v>
+      </c>
+      <c r="W45" s="3">
         <v>100</v>
       </c>
-      <c r="W45" s="3">
-        <v>0</v>
-      </c>
       <c r="X45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
         <v>100</v>
       </c>
-      <c r="Y45" s="3">
-        <v>0</v>
-      </c>
       <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="3">
         <v>100</v>
       </c>
-      <c r="AA45" s="3">
-        <v>0</v>
-      </c>
       <c r="AB45" s="3">
         <v>0</v>
       </c>
@@ -4015,92 +4114,95 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E46" s="3">
         <v>16800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>11400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>12000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>15100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>16900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>18300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>19900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>21500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>300</v>
-      </c>
-      <c r="T46" s="3">
-        <v>100</v>
       </c>
       <c r="U46" s="3">
         <v>100</v>
       </c>
       <c r="V46" s="3">
+        <v>100</v>
+      </c>
+      <c r="W46" s="3">
         <v>200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>600</v>
-      </c>
-      <c r="Y46" s="3">
-        <v>200</v>
       </c>
       <c r="Z46" s="3">
         <v>200</v>
       </c>
       <c r="AA46" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB46" s="3">
         <v>100</v>
       </c>
-      <c r="AB46" s="3">
-        <v>0</v>
-      </c>
       <c r="AC46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="3">
         <v>500</v>
       </c>
-      <c r="AD46" s="3">
-        <v>0</v>
-      </c>
       <c r="AE46" s="3">
         <v>0</v>
       </c>
@@ -4108,13 +4210,16 @@
         <v>0</v>
       </c>
       <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="3">
         <v>100</v>
       </c>
-      <c r="AH46" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4211,13 +4316,16 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E48" s="3">
         <v>500</v>
@@ -4238,13 +4346,13 @@
         <v>500</v>
       </c>
       <c r="K48" s="3">
+        <v>500</v>
+      </c>
+      <c r="L48" s="3">
         <v>600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>500</v>
-      </c>
-      <c r="M48" s="3">
-        <v>400</v>
       </c>
       <c r="N48" s="3">
         <v>400</v>
@@ -4253,7 +4361,7 @@
         <v>400</v>
       </c>
       <c r="P48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Q48" s="3">
         <v>500</v>
@@ -4262,16 +4370,16 @@
         <v>500</v>
       </c>
       <c r="S48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="T48" s="3">
         <v>600</v>
       </c>
       <c r="U48" s="3">
+        <v>600</v>
+      </c>
+      <c r="V48" s="3">
         <v>700</v>
-      </c>
-      <c r="V48" s="3">
-        <v>100</v>
       </c>
       <c r="W48" s="3">
         <v>100</v>
@@ -4280,13 +4388,13 @@
         <v>100</v>
       </c>
       <c r="Y48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z48" s="3">
         <v>200</v>
       </c>
       <c r="AA48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AB48" s="3">
         <v>300</v>
@@ -4295,22 +4403,25 @@
         <v>300</v>
       </c>
       <c r="AD48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AE48" s="3">
         <v>400</v>
       </c>
       <c r="AF48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AG48" s="3">
         <v>500</v>
       </c>
       <c r="AH48" s="3">
+        <v>500</v>
+      </c>
+      <c r="AI48" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4321,10 +4432,10 @@
         <v>700</v>
       </c>
       <c r="F49" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G49" s="3">
         <v>700</v>
-      </c>
-      <c r="G49" s="3">
-        <v>800</v>
       </c>
       <c r="H49" s="3">
         <v>800</v>
@@ -4333,10 +4444,10 @@
         <v>800</v>
       </c>
       <c r="J49" s="3">
+        <v>800</v>
+      </c>
+      <c r="K49" s="3">
         <v>500</v>
-      </c>
-      <c r="K49" s="3">
-        <v>600</v>
       </c>
       <c r="L49" s="3">
         <v>600</v>
@@ -4354,7 +4465,7 @@
         <v>600</v>
       </c>
       <c r="Q49" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="R49" s="3">
         <v>700</v>
@@ -4369,7 +4480,7 @@
         <v>700</v>
       </c>
       <c r="V49" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="W49" s="3">
         <v>800</v>
@@ -4384,7 +4495,7 @@
         <v>800</v>
       </c>
       <c r="AA49" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="AB49" s="3">
         <v>900</v>
@@ -4402,13 +4513,16 @@
         <v>900</v>
       </c>
       <c r="AG49" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AH49" s="3">
         <v>1000</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,16 +4720,19 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
         <v>0</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>4</v>
+      <c r="E52" s="3">
+        <v>0</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>4</v>
@@ -4629,8 +4749,8 @@
       <c r="J52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -4663,14 +4783,14 @@
         <v>0</v>
       </c>
       <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3">
         <v>400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>200</v>
       </c>
-      <c r="X52" s="3">
-        <v>0</v>
-      </c>
       <c r="Y52" s="3">
         <v>0</v>
       </c>
@@ -4687,11 +4807,11 @@
         <v>0</v>
       </c>
       <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="3">
         <v>100</v>
       </c>
-      <c r="AE52" s="3">
-        <v>0</v>
-      </c>
       <c r="AF52" s="3">
         <v>0</v>
       </c>
@@ -4701,8 +4821,11 @@
       <c r="AH52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E54" s="3">
         <v>18000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>13300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>14100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>16400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>19400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>20900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>22500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1400</v>
-      </c>
-      <c r="U54" s="3">
-        <v>1500</v>
       </c>
       <c r="V54" s="3">
         <v>1500</v>
       </c>
       <c r="W54" s="3">
+        <v>1500</v>
+      </c>
+      <c r="X54" s="3">
         <v>2400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1300</v>
-      </c>
-      <c r="AA54" s="3">
-        <v>1200</v>
       </c>
       <c r="AB54" s="3">
         <v>1200</v>
       </c>
       <c r="AC54" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AD54" s="3">
         <v>1800</v>
-      </c>
-      <c r="AD54" s="3">
-        <v>1400</v>
       </c>
       <c r="AE54" s="3">
         <v>1400</v>
       </c>
       <c r="AF54" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AG54" s="3">
         <v>1500</v>
-      </c>
-      <c r="AG54" s="3">
-        <v>1600</v>
       </c>
       <c r="AH54" s="3">
         <v>1600</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,8 +5099,9 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4984,25 +5115,25 @@
         <v>200</v>
       </c>
       <c r="G57" s="3">
+        <v>200</v>
+      </c>
+      <c r="H57" s="3">
         <v>300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>200</v>
-      </c>
-      <c r="M57" s="3">
-        <v>100</v>
       </c>
       <c r="N57" s="3">
         <v>100</v>
@@ -5011,64 +5142,67 @@
         <v>100</v>
       </c>
       <c r="P57" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q57" s="3">
         <v>200</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>100</v>
       </c>
       <c r="R57" s="3">
         <v>100</v>
       </c>
       <c r="S57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T57" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="U57" s="3">
         <v>2000</v>
       </c>
       <c r="V57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="W57" s="3">
         <v>1700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2500</v>
-      </c>
-      <c r="AF57" s="3">
-        <v>2300</v>
       </c>
       <c r="AG57" s="3">
         <v>2300</v>
       </c>
       <c r="AH57" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AI57" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5100,11 +5234,11 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>100</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
@@ -5115,254 +5249,263 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>1100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>8000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>7100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>7500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>5500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>4400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2400</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>1900</v>
       </c>
       <c r="AG58" s="3">
         <v>1900</v>
       </c>
       <c r="AH58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AI58" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E59" s="3">
         <v>3200</v>
       </c>
-      <c r="E59" s="3">
-        <v>900</v>
-      </c>
       <c r="F59" s="3">
+        <v>4000</v>
+      </c>
+      <c r="G59" s="3">
         <v>700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>300</v>
-      </c>
-      <c r="J59" s="3">
-        <v>200</v>
       </c>
       <c r="K59" s="3">
         <v>200</v>
       </c>
       <c r="L59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M59" s="3">
         <v>300</v>
       </c>
       <c r="N59" s="3">
+        <v>300</v>
+      </c>
+      <c r="O59" s="3">
         <v>700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>8300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3600</v>
-      </c>
-      <c r="Y59" s="3">
-        <v>3700</v>
       </c>
       <c r="Z59" s="3">
         <v>3700</v>
       </c>
       <c r="AA59" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AB59" s="3">
         <v>3900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E60" s="3">
         <v>3400</v>
       </c>
-      <c r="E60" s="3">
-        <v>1100</v>
-      </c>
       <c r="F60" s="3">
+        <v>2600</v>
+      </c>
+      <c r="G60" s="3">
         <v>900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>900</v>
-      </c>
-      <c r="O60" s="3">
-        <v>1300</v>
       </c>
       <c r="P60" s="3">
         <v>1300</v>
       </c>
       <c r="Q60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="R60" s="3">
         <v>1000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>18400</v>
-      </c>
-      <c r="U60" s="3">
-        <v>13700</v>
       </c>
       <c r="V60" s="3">
         <v>13700</v>
       </c>
       <c r="W60" s="3">
+        <v>13700</v>
+      </c>
+      <c r="X60" s="3">
         <v>11100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>8700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>8900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>10600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>8800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>8400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>8000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>7000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>6100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5394,23 +5537,23 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4300</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -5421,31 +5564,31 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="W61" s="3">
         <v>200</v>
       </c>
       <c r="X61" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="Y61" s="3">
         <v>500</v>
       </c>
       <c r="Z61" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA61" s="3">
         <v>1200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>200</v>
-      </c>
-      <c r="AD61" s="3">
-        <v>100</v>
       </c>
       <c r="AE61" s="3">
         <v>100</v>
@@ -5454,33 +5597,36 @@
         <v>100</v>
       </c>
       <c r="AG61" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH61" s="3">
         <v>300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E62" s="3">
-        <v>0</v>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F62" s="3">
         <v>0</v>
       </c>
       <c r="G62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H62" s="3">
         <v>100</v>
       </c>
       <c r="I62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J62" s="3">
         <v>200</v>
@@ -5489,7 +5635,7 @@
         <v>200</v>
       </c>
       <c r="L62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M62" s="3">
         <v>300</v>
@@ -5498,7 +5644,7 @@
         <v>300</v>
       </c>
       <c r="O62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="P62" s="3">
         <v>400</v>
@@ -5507,19 +5653,19 @@
         <v>400</v>
       </c>
       <c r="R62" s="3">
+        <v>400</v>
+      </c>
+      <c r="S62" s="3">
         <v>15100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>15200</v>
-      </c>
-      <c r="T62" s="3">
-        <v>500</v>
       </c>
       <c r="U62" s="3">
         <v>500</v>
       </c>
       <c r="V62" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="W62" s="3">
         <v>0</v>
@@ -5528,13 +5674,13 @@
         <v>0</v>
       </c>
       <c r="Y62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z62" s="3">
         <v>100</v>
       </c>
       <c r="AA62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB62" s="3">
         <v>0</v>
@@ -5552,13 +5698,16 @@
         <v>0</v>
       </c>
       <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="3">
         <v>400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E66" s="3">
         <v>3400</v>
       </c>
-      <c r="E66" s="3">
-        <v>1100</v>
-      </c>
       <c r="F66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="G66" s="3">
         <v>1000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>900</v>
-      </c>
-      <c r="H66" s="3">
-        <v>600</v>
       </c>
       <c r="I66" s="3">
         <v>600</v>
       </c>
       <c r="J66" s="3">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="K66" s="3">
         <v>900</v>
       </c>
       <c r="L66" s="3">
+        <v>900</v>
+      </c>
+      <c r="M66" s="3">
         <v>800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>16500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>16100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>18900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>14200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>13900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>11400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>10200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>11100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>8900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>8600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>8100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>7100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-153000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-148900</v>
       </c>
-      <c r="E72" s="3">
-        <v>-167100</v>
-      </c>
       <c r="F72" s="3">
+        <v>-146700</v>
+      </c>
+      <c r="G72" s="3">
         <v>-164200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-161300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-158300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-152600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-148300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-143600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-139000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-134100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-113700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-109600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-105500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-89800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-84100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-83200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-86100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-78600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-77000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-72000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-67800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-63900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-60400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-57400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-53900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-51400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-49500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-47500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-44700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-42000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-39900</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E76" s="3">
         <v>14500</v>
       </c>
-      <c r="E76" s="3">
-        <v>11500</v>
-      </c>
       <c r="F76" s="3">
+        <v>10000</v>
+      </c>
+      <c r="G76" s="3">
         <v>12800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>15800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>17000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>18600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>21600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-4900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-3800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-1300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-15100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-14400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-17500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-12800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-12400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-8900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-7700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-8600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-8900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-9900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-7700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-6800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-6700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-5700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-4700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-5000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>4</v>
+      <c r="D81" s="3">
+        <v>-4000</v>
       </c>
       <c r="E81" s="3">
-        <v>-2800</v>
+        <v>-2200</v>
       </c>
       <c r="F81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G81" s="3">
         <v>-2900</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-3000</v>
       </c>
       <c r="H81" s="3">
         <v>-5700</v>
       </c>
       <c r="I81" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="J81" s="3">
         <v>-4300</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-4700</v>
       </c>
       <c r="K81" s="3">
         <v>-4700</v>
       </c>
       <c r="L81" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="M81" s="3">
         <v>-4800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-20400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-15700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-5800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-7600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-5100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-4200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-2700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-2100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7253,13 +7452,13 @@
         <v>0</v>
       </c>
       <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3">
         <v>100</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
-      </c>
       <c r="U83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V83" s="3">
         <v>100</v>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,31 +8144,32 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
@@ -7957,13 +8178,13 @@
         <v>-100</v>
       </c>
       <c r="M91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>4</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>4</v>
@@ -7971,8 +8192,8 @@
       <c r="Q91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="R91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -7986,20 +8207,20 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>4</v>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>4</v>
+      <c r="AA91" s="3">
+        <v>0</v>
       </c>
       <c r="AB91" s="3" t="s">
         <v>4</v>
@@ -8016,14 +8237,17 @@
       <c r="AF91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG91" s="3">
-        <v>0</v>
+      <c r="AG91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,40 +8445,43 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>100</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
-        <v>700</v>
+        <v>-200</v>
       </c>
       <c r="H94" s="3">
+        <v>800</v>
+      </c>
+      <c r="I94" s="3">
         <v>2500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9900</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-100</v>
       </c>
       <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>4</v>
+      <c r="M94" s="3">
+        <v>-100</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>4</v>
@@ -8265,8 +8495,8 @@
       <c r="Q94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
+      <c r="R94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S94" s="3">
         <v>0</v>
@@ -8280,26 +8510,26 @@
       <c r="V94" s="3">
         <v>0</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>4</v>
+      <c r="W94" s="3">
+        <v>0</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
+      <c r="Y94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>4</v>
+      <c r="AA94" s="3">
+        <v>0</v>
       </c>
       <c r="AB94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
+      <c r="AC94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD94" s="3">
         <v>0</v>
@@ -8316,8 +8546,11 @@
       <c r="AH94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,26 +8987,29 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>7500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>400</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
@@ -8777,73 +9023,76 @@
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>21100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>3500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8940,92 +9189,95 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E102" s="3">
         <v>300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-11400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>19900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>300</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
       <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
         <v>-100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>400</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
-      </c>
       <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>100</v>
       </c>
-      <c r="AA102" s="3">
-        <v>0</v>
-      </c>
       <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
         <v>-400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>500</v>
       </c>
-      <c r="AD102" s="3">
-        <v>0</v>
-      </c>
       <c r="AE102" s="3">
         <v>0</v>
       </c>
@@ -9036,6 +9288,9 @@
         <v>0</v>
       </c>
       <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>-500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BRTX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BRTX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="92">
   <si>
     <t>BRTX</t>
   </si>
@@ -656,160 +656,164 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>200</v>
+      </c>
+      <c r="E8" s="3">
         <v>100</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
       <c r="F8" s="3">
         <v>0</v>
       </c>
@@ -817,11 +821,11 @@
         <v>0</v>
       </c>
       <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
         <v>100</v>
       </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
       <c r="J8" s="3">
         <v>0</v>
       </c>
@@ -829,11 +833,11 @@
         <v>0</v>
       </c>
       <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
         <v>100</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
       <c r="N8" s="3">
         <v>0</v>
       </c>
@@ -900,16 +904,19 @@
       <c r="AI8" s="3">
         <v>0</v>
       </c>
+      <c r="AJ8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>4</v>
+      <c r="E9" s="3">
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>4</v>
@@ -995,37 +1002,40 @@
       <c r="AG9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH9" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="3" t="s">
+      <c r="AH9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>200</v>
+      </c>
+      <c r="E10" s="3">
         <v>100</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>4</v>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>100</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>4</v>
@@ -1096,14 +1106,17 @@
       <c r="AG10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI10" s="3" t="s">
+      <c r="AH10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1148,34 +1162,34 @@
         <v>1300</v>
       </c>
       <c r="E12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F12" s="3">
         <v>1100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
+        <v>800</v>
+      </c>
+      <c r="I12" s="3">
         <v>900</v>
       </c>
-      <c r="H12" s="3">
-        <v>900</v>
-      </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>800</v>
-      </c>
-      <c r="N12" s="3">
-        <v>200</v>
       </c>
       <c r="O12" s="3">
         <v>200</v>
@@ -1190,16 +1204,16 @@
         <v>200</v>
       </c>
       <c r="S12" s="3">
+        <v>200</v>
+      </c>
+      <c r="T12" s="3">
         <v>300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>200</v>
-      </c>
-      <c r="V12" s="3">
-        <v>400</v>
       </c>
       <c r="W12" s="3">
         <v>400</v>
@@ -1208,10 +1222,10 @@
         <v>400</v>
       </c>
       <c r="Y12" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z12" s="3">
         <v>500</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>400</v>
       </c>
       <c r="AA12" s="3">
         <v>400</v>
@@ -1223,25 +1237,28 @@
         <v>400</v>
       </c>
       <c r="AD12" s="3">
+        <v>400</v>
+      </c>
+      <c r="AE12" s="3">
         <v>200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>600</v>
-      </c>
-      <c r="AG12" s="3">
-        <v>800</v>
       </c>
       <c r="AH12" s="3">
         <v>800</v>
       </c>
       <c r="AI12" s="3">
+        <v>800</v>
+      </c>
+      <c r="AJ12" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,8 +1358,11 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1355,17 +1375,17 @@
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1374,14 +1394,14 @@
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>16200</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1389,38 +1409,38 @@
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>4700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>3200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>300</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
@@ -1434,16 +1454,19 @@
         <v>0</v>
       </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>100</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E17" s="3">
         <v>2600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>20200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>15100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1800</v>
-      </c>
-      <c r="AF17" s="3">
-        <v>2600</v>
       </c>
       <c r="AG17" s="3">
         <v>2600</v>
       </c>
       <c r="AH17" s="3">
+        <v>2600</v>
+      </c>
+      <c r="AI17" s="3">
         <v>1900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-4100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3200</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-3100</v>
       </c>
       <c r="H18" s="3">
         <v>-3100</v>
       </c>
       <c r="I18" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="J18" s="3">
         <v>-5800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-4700</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-4600</v>
       </c>
       <c r="L18" s="3">
         <v>-4600</v>
       </c>
       <c r="M18" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="N18" s="3">
         <v>-4800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-20200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-15100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-5600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-4100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-1800</v>
-      </c>
-      <c r="AF18" s="3">
-        <v>-2600</v>
       </c>
       <c r="AG18" s="3">
         <v>-2600</v>
       </c>
       <c r="AH18" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="AI18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,35 +1849,36 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1600</v>
+        <v>-1000</v>
       </c>
       <c r="E20" s="3">
-        <v>1900</v>
+        <v>1700</v>
       </c>
       <c r="F20" s="3">
-        <v>4400</v>
+        <v>-1700</v>
       </c>
       <c r="G20" s="3">
-        <v>200</v>
+        <v>-4000</v>
       </c>
       <c r="H20" s="3">
-        <v>-2600</v>
+        <v>-7800</v>
       </c>
       <c r="I20" s="3">
-        <v>-1400</v>
+        <v>2700</v>
       </c>
       <c r="J20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1870,40 +1904,40 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
-        <v>-2100</v>
+        <v>0</v>
       </c>
       <c r="U20" s="3">
         <v>-2100</v>
       </c>
       <c r="V20" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="W20" s="3">
         <v>1100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>200</v>
       </c>
       <c r="AD20" s="3">
         <v>200</v>
       </c>
       <c r="AE20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AF20" s="3">
         <v>0</v>
@@ -1917,73 +1951,76 @@
       <c r="AI20" s="3">
         <v>0</v>
       </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-4000</v>
+        <v>-1200</v>
       </c>
       <c r="E21" s="3">
-        <v>-2200</v>
+        <v>-4200</v>
       </c>
       <c r="F21" s="3">
-        <v>1200</v>
+        <v>-2300</v>
       </c>
       <c r="G21" s="3">
-        <v>-2900</v>
+        <v>800</v>
       </c>
       <c r="H21" s="3">
-        <v>-5700</v>
+        <v>4700</v>
       </c>
       <c r="I21" s="3">
-        <v>-7100</v>
+        <v>-5800</v>
       </c>
       <c r="J21" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="K21" s="3">
         <v>-4300</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-4600</v>
       </c>
       <c r="L21" s="3">
         <v>-4600</v>
       </c>
       <c r="M21" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="N21" s="3">
         <v>-4800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-20200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-3700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-15000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-5500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-3200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-6200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-3100</v>
-      </c>
-      <c r="X21" s="3">
-        <v>-2800</v>
       </c>
       <c r="Y21" s="3">
         <v>-2800</v>
@@ -1992,34 +2029,37 @@
         <v>-2800</v>
       </c>
       <c r="AA21" s="3">
-        <v>-2100</v>
+        <v>-2800</v>
       </c>
       <c r="AB21" s="3">
         <v>-2100</v>
       </c>
       <c r="AC21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="AD21" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-1700</v>
-      </c>
-      <c r="AF21" s="3">
-        <v>-2500</v>
       </c>
       <c r="AG21" s="3">
         <v>-2500</v>
       </c>
       <c r="AH21" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="AI21" s="3">
         <v>-1800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2044,8 +2084,8 @@
       <c r="J22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2054,61 +2094,61 @@
         <v>0</v>
       </c>
       <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
         <v>200</v>
-      </c>
-      <c r="O22" s="3">
-        <v>500</v>
       </c>
       <c r="P22" s="3">
         <v>500</v>
       </c>
       <c r="Q22" s="3">
+        <v>500</v>
+      </c>
+      <c r="R22" s="3">
         <v>600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>200</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
       <c r="T22" s="3">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="U22" s="3">
         <v>1400</v>
       </c>
       <c r="V22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="W22" s="3">
         <v>900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>1100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1300</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>400</v>
       </c>
       <c r="AD22" s="3">
         <v>400</v>
       </c>
       <c r="AE22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AF22" s="3">
         <v>300</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>200</v>
       </c>
       <c r="AG22" s="3">
         <v>200</v>
@@ -2117,134 +2157,140 @@
         <v>200</v>
       </c>
       <c r="AI22" s="3">
+        <v>200</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1200</v>
       </c>
-      <c r="G23" s="3">
-        <v>-2900</v>
-      </c>
       <c r="H23" s="3">
+        <v>4800</v>
+      </c>
+      <c r="I23" s="3">
         <v>-5700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-4300</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-4700</v>
       </c>
       <c r="L23" s="3">
         <v>-4700</v>
       </c>
       <c r="M23" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="N23" s="3">
         <v>-4800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-20400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-15700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-5800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-7600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-5100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-2700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-2100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -2321,8 +2367,11 @@
       <c r="AI24" s="3">
         <v>0</v>
       </c>
+      <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1200</v>
       </c>
-      <c r="G26" s="3">
-        <v>-2900</v>
-      </c>
       <c r="H26" s="3">
+        <v>4800</v>
+      </c>
+      <c r="I26" s="3">
         <v>-5700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4300</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-4700</v>
       </c>
       <c r="L26" s="3">
         <v>-4700</v>
       </c>
       <c r="M26" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="N26" s="3">
         <v>-4800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-20400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-15700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-5800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-4700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-7600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-5100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-2700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-2100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1200</v>
       </c>
-      <c r="G27" s="3">
-        <v>-2900</v>
-      </c>
       <c r="H27" s="3">
+        <v>4800</v>
+      </c>
+      <c r="I27" s="3">
         <v>-5700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-7200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4300</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-4700</v>
       </c>
       <c r="L27" s="3">
         <v>-4700</v>
       </c>
       <c r="M27" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="N27" s="3">
         <v>-4800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-20400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-15700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-5800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-7600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-5100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-2700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-2100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,35 +3095,38 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1600</v>
+        <v>1000</v>
       </c>
       <c r="E32" s="3">
-        <v>-1900</v>
+        <v>-1700</v>
       </c>
       <c r="F32" s="3">
-        <v>-4400</v>
+        <v>1700</v>
       </c>
       <c r="G32" s="3">
-        <v>-200</v>
+        <v>4000</v>
       </c>
       <c r="H32" s="3">
-        <v>2600</v>
+        <v>7800</v>
       </c>
       <c r="I32" s="3">
-        <v>1400</v>
+        <v>-2700</v>
       </c>
       <c r="J32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -3082,40 +3152,40 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="U32" s="3">
         <v>2100</v>
       </c>
       <c r="V32" s="3">
+        <v>2100</v>
+      </c>
+      <c r="W32" s="3">
         <v>-1100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>100</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>-200</v>
       </c>
       <c r="AD32" s="3">
         <v>-200</v>
       </c>
       <c r="AE32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="AF32" s="3">
         <v>0</v>
@@ -3129,109 +3199,115 @@
       <c r="AI32" s="3">
         <v>0</v>
       </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1200</v>
       </c>
-      <c r="G33" s="3">
-        <v>-2900</v>
-      </c>
       <c r="H33" s="3">
+        <v>4800</v>
+      </c>
+      <c r="I33" s="3">
         <v>-5700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-7200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4300</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-4700</v>
       </c>
       <c r="L33" s="3">
         <v>-4700</v>
       </c>
       <c r="M33" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="N33" s="3">
         <v>-4800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-20400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-15700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-5800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-7600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-5100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-2700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-2100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1200</v>
       </c>
-      <c r="G35" s="3">
-        <v>-2900</v>
-      </c>
       <c r="H35" s="3">
+        <v>4800</v>
+      </c>
+      <c r="I35" s="3">
         <v>-5700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-7200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4300</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-4700</v>
       </c>
       <c r="L35" s="3">
         <v>-4700</v>
       </c>
       <c r="M35" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="N35" s="3">
         <v>-4800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-20400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-15700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-5800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-7600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-5100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-2700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-2100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,95 +3698,96 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E41" s="3">
         <v>2300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2400</v>
-      </c>
-      <c r="H41" s="3">
-        <v>1800</v>
       </c>
       <c r="I41" s="3">
         <v>1800</v>
       </c>
       <c r="J41" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K41" s="3">
         <v>1700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>17900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>19300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>21000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>300</v>
       </c>
-      <c r="U41" s="3">
-        <v>0</v>
-      </c>
       <c r="V41" s="3">
         <v>0</v>
       </c>
       <c r="W41" s="3">
+        <v>0</v>
+      </c>
+      <c r="X41" s="3">
         <v>100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>500</v>
-      </c>
-      <c r="Z41" s="3">
-        <v>100</v>
       </c>
       <c r="AA41" s="3">
         <v>100</v>
       </c>
       <c r="AB41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC41" s="3">
         <v>0</v>
       </c>
       <c r="AD41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE41" s="3">
         <v>500</v>
       </c>
-      <c r="AE41" s="3">
-        <v>0</v>
-      </c>
       <c r="AF41" s="3">
         <v>0</v>
       </c>
@@ -3713,38 +3800,41 @@
       <c r="AI41" s="3">
         <v>0</v>
       </c>
+      <c r="AJ41" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E42" s="3">
         <v>12400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>15300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>10200</v>
-      </c>
-      <c r="G42" s="3">
-        <v>9800</v>
       </c>
       <c r="H42" s="3">
         <v>9800</v>
       </c>
       <c r="I42" s="3">
+        <v>9800</v>
+      </c>
+      <c r="J42" s="3">
         <v>10500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>13100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>9900</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3760,8 +3850,8 @@
       <c r="Q42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -3814,13 +3904,16 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E43" s="3">
         <v>0</v>
@@ -3915,31 +4008,34 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -4016,31 +4112,34 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>300</v>
-      </c>
-      <c r="E45" s="3">
-        <v>300</v>
-      </c>
-      <c r="F45" s="3">
-        <v>300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>300</v>
-      </c>
-      <c r="H45" s="3">
-        <v>400</v>
-      </c>
-      <c r="I45" s="3">
-        <v>400</v>
-      </c>
-      <c r="J45" s="3">
-        <v>400</v>
+        <v>0</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K45" s="3">
         <v>400</v>
@@ -4049,16 +4148,16 @@
         <v>400</v>
       </c>
       <c r="M45" s="3">
+        <v>400</v>
+      </c>
+      <c r="N45" s="3">
         <v>500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>400</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
       <c r="P45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q45" s="3">
         <v>100</v>
@@ -4067,7 +4166,7 @@
         <v>100</v>
       </c>
       <c r="S45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T45" s="3">
         <v>0</v>
@@ -4079,23 +4178,23 @@
         <v>0</v>
       </c>
       <c r="W45" s="3">
+        <v>0</v>
+      </c>
+      <c r="X45" s="3">
         <v>100</v>
       </c>
-      <c r="X45" s="3">
-        <v>0</v>
-      </c>
       <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="3">
         <v>100</v>
       </c>
-      <c r="Z45" s="3">
-        <v>0</v>
-      </c>
       <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="3">
         <v>100</v>
       </c>
-      <c r="AB45" s="3">
-        <v>0</v>
-      </c>
       <c r="AC45" s="3">
         <v>0</v>
       </c>
@@ -4117,95 +4216,98 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E46" s="3">
         <v>15000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>16800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>11400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>12600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>15100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>16900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>18300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>19900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>21500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>300</v>
-      </c>
-      <c r="U46" s="3">
-        <v>100</v>
       </c>
       <c r="V46" s="3">
         <v>100</v>
       </c>
       <c r="W46" s="3">
+        <v>100</v>
+      </c>
+      <c r="X46" s="3">
         <v>200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>600</v>
-      </c>
-      <c r="Z46" s="3">
-        <v>200</v>
       </c>
       <c r="AA46" s="3">
         <v>200</v>
       </c>
       <c r="AB46" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC46" s="3">
         <v>100</v>
       </c>
-      <c r="AC46" s="3">
-        <v>0</v>
-      </c>
       <c r="AD46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE46" s="3">
         <v>500</v>
       </c>
-      <c r="AE46" s="3">
-        <v>0</v>
-      </c>
       <c r="AF46" s="3">
         <v>0</v>
       </c>
@@ -4213,36 +4315,39 @@
         <v>0</v>
       </c>
       <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI46" s="3">
         <v>100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4319,8 +4424,11 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4328,7 +4436,7 @@
         <v>400</v>
       </c>
       <c r="E48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F48" s="3">
         <v>500</v>
@@ -4349,13 +4457,13 @@
         <v>500</v>
       </c>
       <c r="L48" s="3">
+        <v>500</v>
+      </c>
+      <c r="M48" s="3">
         <v>600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>500</v>
-      </c>
-      <c r="N48" s="3">
-        <v>400</v>
       </c>
       <c r="O48" s="3">
         <v>400</v>
@@ -4364,7 +4472,7 @@
         <v>400</v>
       </c>
       <c r="Q48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="R48" s="3">
         <v>500</v>
@@ -4373,16 +4481,16 @@
         <v>500</v>
       </c>
       <c r="T48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="U48" s="3">
         <v>600</v>
       </c>
       <c r="V48" s="3">
+        <v>600</v>
+      </c>
+      <c r="W48" s="3">
         <v>700</v>
-      </c>
-      <c r="W48" s="3">
-        <v>100</v>
       </c>
       <c r="X48" s="3">
         <v>100</v>
@@ -4391,13 +4499,13 @@
         <v>100</v>
       </c>
       <c r="Z48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA48" s="3">
         <v>200</v>
       </c>
       <c r="AB48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AC48" s="3">
         <v>300</v>
@@ -4406,39 +4514,42 @@
         <v>300</v>
       </c>
       <c r="AE48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AF48" s="3">
         <v>400</v>
       </c>
       <c r="AG48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AH48" s="3">
         <v>500</v>
       </c>
       <c r="AI48" s="3">
+        <v>500</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E49" s="3">
         <v>700</v>
       </c>
       <c r="F49" s="3">
-        <v>1400</v>
+        <v>700</v>
       </c>
       <c r="G49" s="3">
         <v>700</v>
       </c>
       <c r="H49" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="I49" s="3">
         <v>800</v>
@@ -4447,10 +4558,10 @@
         <v>800</v>
       </c>
       <c r="K49" s="3">
+        <v>800</v>
+      </c>
+      <c r="L49" s="3">
         <v>500</v>
-      </c>
-      <c r="L49" s="3">
-        <v>600</v>
       </c>
       <c r="M49" s="3">
         <v>600</v>
@@ -4468,7 +4579,7 @@
         <v>600</v>
       </c>
       <c r="R49" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="S49" s="3">
         <v>700</v>
@@ -4483,7 +4594,7 @@
         <v>700</v>
       </c>
       <c r="W49" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="X49" s="3">
         <v>800</v>
@@ -4498,7 +4609,7 @@
         <v>800</v>
       </c>
       <c r="AB49" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="AC49" s="3">
         <v>900</v>
@@ -4516,13 +4627,16 @@
         <v>900</v>
       </c>
       <c r="AH49" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AI49" s="3">
         <v>1000</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,16 +4840,19 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>4</v>
@@ -4752,8 +4872,8 @@
       <c r="K52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -4786,14 +4906,14 @@
         <v>0</v>
       </c>
       <c r="W52" s="3">
+        <v>0</v>
+      </c>
+      <c r="X52" s="3">
         <v>400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>200</v>
       </c>
-      <c r="Y52" s="3">
-        <v>0</v>
-      </c>
       <c r="Z52" s="3">
         <v>0</v>
       </c>
@@ -4810,11 +4930,11 @@
         <v>0</v>
       </c>
       <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="3">
         <v>100</v>
       </c>
-      <c r="AF52" s="3">
-        <v>0</v>
-      </c>
       <c r="AG52" s="3">
         <v>0</v>
       </c>
@@ -4824,8 +4944,11 @@
       <c r="AI52" s="3">
         <v>0</v>
       </c>
+      <c r="AJ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E54" s="3">
         <v>16100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>18000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>12600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>13800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>13300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>14100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>16400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>17900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>19400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>20900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>22500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1400</v>
-      </c>
-      <c r="V54" s="3">
-        <v>1500</v>
       </c>
       <c r="W54" s="3">
         <v>1500</v>
       </c>
       <c r="X54" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Y54" s="3">
         <v>2400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1300</v>
-      </c>
-      <c r="AB54" s="3">
-        <v>1200</v>
       </c>
       <c r="AC54" s="3">
         <v>1200</v>
       </c>
       <c r="AD54" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AE54" s="3">
         <v>1800</v>
-      </c>
-      <c r="AE54" s="3">
-        <v>1400</v>
       </c>
       <c r="AF54" s="3">
         <v>1400</v>
       </c>
       <c r="AG54" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AH54" s="3">
         <v>1500</v>
-      </c>
-      <c r="AH54" s="3">
-        <v>1600</v>
       </c>
       <c r="AI54" s="3">
         <v>1600</v>
       </c>
+      <c r="AJ54" s="3">
+        <v>1600</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,13 +5230,14 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="E57" s="3">
         <v>200</v>
@@ -5118,25 +5249,25 @@
         <v>200</v>
       </c>
       <c r="H57" s="3">
+        <v>200</v>
+      </c>
+      <c r="I57" s="3">
         <v>300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>200</v>
-      </c>
-      <c r="N57" s="3">
-        <v>100</v>
       </c>
       <c r="O57" s="3">
         <v>100</v>
@@ -5145,64 +5276,67 @@
         <v>100</v>
       </c>
       <c r="Q57" s="3">
+        <v>100</v>
+      </c>
+      <c r="R57" s="3">
         <v>200</v>
-      </c>
-      <c r="R57" s="3">
-        <v>100</v>
       </c>
       <c r="S57" s="3">
         <v>100</v>
       </c>
       <c r="T57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U57" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="V57" s="3">
         <v>2000</v>
       </c>
       <c r="W57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="X57" s="3">
         <v>1700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2500</v>
-      </c>
-      <c r="AG57" s="3">
-        <v>2300</v>
       </c>
       <c r="AH57" s="3">
         <v>2300</v>
       </c>
       <c r="AI57" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AJ57" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5210,22 +5344,22 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5237,11 +5371,11 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>100</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -5252,260 +5386,269 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>1100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>8000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>7100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>7500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>4400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2400</v>
-      </c>
-      <c r="AG58" s="3">
-        <v>1900</v>
       </c>
       <c r="AH58" s="3">
         <v>1900</v>
       </c>
       <c r="AI58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5100</v>
+        <v>3500</v>
       </c>
       <c r="E59" s="3">
-        <v>3200</v>
+        <v>4600</v>
       </c>
       <c r="F59" s="3">
-        <v>4000</v>
+        <v>2800</v>
       </c>
       <c r="G59" s="3">
-        <v>700</v>
-      </c>
-      <c r="H59" s="3">
-        <v>500</v>
-      </c>
-      <c r="I59" s="3">
-        <v>400</v>
-      </c>
-      <c r="J59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K59" s="3">
         <v>300</v>
-      </c>
-      <c r="K59" s="3">
-        <v>200</v>
       </c>
       <c r="L59" s="3">
         <v>200</v>
       </c>
       <c r="M59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N59" s="3">
         <v>300</v>
       </c>
       <c r="O59" s="3">
+        <v>300</v>
+      </c>
+      <c r="P59" s="3">
         <v>700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3600</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>3700</v>
       </c>
       <c r="AA59" s="3">
         <v>3700</v>
       </c>
       <c r="AB59" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AC59" s="3">
         <v>3900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E60" s="3">
         <v>5300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>900</v>
-      </c>
-      <c r="P60" s="3">
-        <v>1300</v>
       </c>
       <c r="Q60" s="3">
         <v>1300</v>
       </c>
       <c r="R60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="S60" s="3">
         <v>1000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>18400</v>
-      </c>
-      <c r="V60" s="3">
-        <v>13700</v>
       </c>
       <c r="W60" s="3">
         <v>13700</v>
       </c>
       <c r="X60" s="3">
+        <v>13700</v>
+      </c>
+      <c r="Y60" s="3">
         <v>11100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>8700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>9300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>8900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>10600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>8800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>8400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>6100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>5800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5525,10 +5668,10 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -5540,23 +5683,23 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4300</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -5567,31 +5710,31 @@
         <v>0</v>
       </c>
       <c r="W61" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="X61" s="3">
         <v>200</v>
       </c>
       <c r="Y61" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="Z61" s="3">
         <v>500</v>
       </c>
       <c r="AA61" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB61" s="3">
         <v>1200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>200</v>
-      </c>
-      <c r="AE61" s="3">
-        <v>100</v>
       </c>
       <c r="AF61" s="3">
         <v>100</v>
@@ -5600,13 +5743,16 @@
         <v>100</v>
       </c>
       <c r="AH61" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI61" s="3">
         <v>300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5616,20 +5762,20 @@
       <c r="E62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>100</v>
-      </c>
-      <c r="I62" s="3">
-        <v>100</v>
-      </c>
-      <c r="J62" s="3">
-        <v>200</v>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K62" s="3">
         <v>200</v>
@@ -5638,7 +5784,7 @@
         <v>200</v>
       </c>
       <c r="M62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N62" s="3">
         <v>300</v>
@@ -5647,7 +5793,7 @@
         <v>300</v>
       </c>
       <c r="P62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="Q62" s="3">
         <v>400</v>
@@ -5656,19 +5802,19 @@
         <v>400</v>
       </c>
       <c r="S62" s="3">
+        <v>400</v>
+      </c>
+      <c r="T62" s="3">
         <v>15100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>15200</v>
-      </c>
-      <c r="U62" s="3">
-        <v>500</v>
       </c>
       <c r="V62" s="3">
         <v>500</v>
       </c>
       <c r="W62" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="X62" s="3">
         <v>0</v>
@@ -5677,13 +5823,13 @@
         <v>0</v>
       </c>
       <c r="Z62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA62" s="3">
         <v>100</v>
       </c>
       <c r="AB62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC62" s="3">
         <v>0</v>
@@ -5701,13 +5847,16 @@
         <v>0</v>
       </c>
       <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI62" s="3">
         <v>400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E66" s="3">
         <v>5300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>900</v>
-      </c>
-      <c r="I66" s="3">
-        <v>600</v>
       </c>
       <c r="J66" s="3">
         <v>600</v>
       </c>
       <c r="K66" s="3">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="L66" s="3">
         <v>900</v>
       </c>
       <c r="M66" s="3">
+        <v>900</v>
+      </c>
+      <c r="N66" s="3">
         <v>800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>6400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>16500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>16100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>18900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>14200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>13900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>11400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>9800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>10200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>11100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>8900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>8600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>8100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>7100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-154000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-153000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-148900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-146700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-164200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-161300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-158300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-152600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-148300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-143600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-139000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-134100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-113700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-109600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-105500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-89800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-84100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-83200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-86100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-78600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-77000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-72000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-67800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-63900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-60400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-57400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-53900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-51400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-49500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-47500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-44700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-42000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-39900</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E76" s="3">
         <v>10800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>14500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>15800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>17000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>18600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>21600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-4900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-2700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-1300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-15100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-14400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-17500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-12800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-12400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-8900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-7700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-8600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-8900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-9900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-7700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-6800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-6700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-5700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-4700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-5000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1200</v>
       </c>
-      <c r="G81" s="3">
-        <v>-2900</v>
-      </c>
       <c r="H81" s="3">
+        <v>4800</v>
+      </c>
+      <c r="I81" s="3">
         <v>-5700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-7200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4300</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-4700</v>
       </c>
       <c r="L81" s="3">
         <v>-4700</v>
       </c>
       <c r="M81" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="N81" s="3">
         <v>-4800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-20400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-15700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-5800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-7600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-5100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-2700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-2100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,8 +7599,9 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7455,13 +7654,13 @@
         <v>0</v>
       </c>
       <c r="T83" s="3">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3">
         <v>100</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
-      </c>
       <c r="V83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W83" s="3">
         <v>100</v>
@@ -7502,8 +7701,11 @@
       <c r="AI83" s="3">
         <v>100</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="K89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="L89" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="M89" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="N89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="O89" s="3">
         <v>-1100</v>
       </c>
-      <c r="I89" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="P89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="R89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="S89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="T89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="U89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="V89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="W89" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="X89" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="Y89" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="Z89" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-1600</v>
       </c>
-      <c r="K89" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="AB89" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="AC89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AD89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AE89" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="AF89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AG89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AH89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AI89" s="3">
         <v>-1100</v>
       </c>
-      <c r="O89" s="3">
-        <v>-600</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-700</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>-800</v>
-      </c>
-      <c r="R89" s="3">
-        <v>-600</v>
-      </c>
-      <c r="S89" s="3">
-        <v>-500</v>
-      </c>
-      <c r="T89" s="3">
-        <v>-900</v>
-      </c>
-      <c r="U89" s="3">
-        <v>-400</v>
-      </c>
-      <c r="V89" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="W89" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="X89" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="AA89" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="AB89" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="AC89" s="3">
+      <c r="AJ89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD89" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="AE89" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AF89" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AG89" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="AH89" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="AI89" s="3">
-        <v>-1200</v>
-      </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,34 +8365,35 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L91" s="3">
         <v>-100</v>
@@ -8181,13 +8402,13 @@
         <v>-100</v>
       </c>
       <c r="N91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>4</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>4</v>
@@ -8195,8 +8416,8 @@
       <c r="R91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
+      <c r="S91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
@@ -8210,20 +8431,20 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>4</v>
+      <c r="X91" s="3">
+        <v>0</v>
       </c>
       <c r="Y91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
+      <c r="Z91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>4</v>
+      <c r="AB91" s="3">
+        <v>0</v>
       </c>
       <c r="AC91" s="3" t="s">
         <v>4</v>
@@ -8240,14 +8461,17 @@
       <c r="AG91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH91" s="3">
-        <v>0</v>
+      <c r="AH91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AI91" s="3">
         <v>0</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,43 +8675,46 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>900</v>
+      </c>
+      <c r="E94" s="3">
         <v>3000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>100</v>
       </c>
-      <c r="G94" s="3">
-        <v>-200</v>
-      </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>2500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9900</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-100</v>
       </c>
       <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>4</v>
+      <c r="N94" s="3">
+        <v>-100</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>4</v>
@@ -8498,8 +8728,8 @@
       <c r="R94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
+      <c r="S94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T94" s="3">
         <v>0</v>
@@ -8513,26 +8743,26 @@
       <c r="W94" s="3">
         <v>0</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>4</v>
+      <c r="X94" s="3">
+        <v>0</v>
       </c>
       <c r="Y94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
+      <c r="Z94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>4</v>
+      <c r="AB94" s="3">
+        <v>0</v>
       </c>
       <c r="AC94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD94" s="3">
-        <v>0</v>
+      <c r="AD94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE94" s="3">
         <v>0</v>
@@ -8549,8 +8779,11 @@
       <c r="AI94" s="3">
         <v>0</v>
       </c>
+      <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,31 +8819,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,8 +9233,11 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8999,22 +9245,22 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>7500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>400</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="J100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -9026,96 +9272,99 @@
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>21100</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>3500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>1100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9192,95 +9441,98 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E102" s="3">
         <v>1100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-11400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>19900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>300</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
       <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3">
         <v>-100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>400</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
-      </c>
       <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>100</v>
       </c>
-      <c r="AB102" s="3">
-        <v>0</v>
-      </c>
       <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
         <v>-400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>500</v>
       </c>
-      <c r="AE102" s="3">
-        <v>0</v>
-      </c>
       <c r="AF102" s="3">
         <v>0</v>
       </c>
@@ -9291,6 +9543,9 @@
         <v>0</v>
       </c>
       <c r="AI102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>-500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BRTX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BRTX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="92">
   <si>
     <t>BRTX</t>
   </si>
@@ -656,194 +656,201 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
         <v>200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>100</v>
       </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
       <c r="H8" s="3">
         <v>0</v>
       </c>
       <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3">
         <v>100</v>
       </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
       <c r="L8" s="3">
         <v>0</v>
       </c>
       <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
         <v>100</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
       <c r="P8" s="3">
         <v>0</v>
       </c>
@@ -907,8 +914,14 @@
       <c r="AJ8" s="3">
         <v>0</v>
       </c>
+      <c r="AK8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -918,11 +931,11 @@
       <c r="E9" s="3">
         <v>0</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>4</v>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>4</v>
@@ -1005,43 +1018,49 @@
       <c r="AH9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI9" s="3">
-        <v>0</v>
+      <c r="AI9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AJ9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
         <v>200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>100</v>
       </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
-      <c r="G10" s="3">
-        <v>0</v>
-      </c>
       <c r="H10" s="3">
         <v>0</v>
       </c>
       <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3">
         <v>100</v>
       </c>
-      <c r="J10" s="3">
-        <v>0</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>4</v>
+      <c r="L10" s="3">
+        <v>0</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>4</v>
@@ -1109,14 +1128,20 @@
       <c r="AH10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI10" s="3">
-        <v>0</v>
+      <c r="AI10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AJ10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1153,49 +1178,51 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F12" s="3">
         <v>1300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>1300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>1100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J12" s="3">
+        <v>800</v>
+      </c>
+      <c r="K12" s="3">
+        <v>900</v>
+      </c>
+      <c r="L12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="M12" s="3">
         <v>700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="N12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="P12" s="3">
         <v>800</v>
-      </c>
-      <c r="I12" s="3">
-        <v>900</v>
-      </c>
-      <c r="J12" s="3">
-        <v>1200</v>
-      </c>
-      <c r="K12" s="3">
-        <v>700</v>
-      </c>
-      <c r="L12" s="3">
-        <v>1000</v>
-      </c>
-      <c r="M12" s="3">
-        <v>1100</v>
-      </c>
-      <c r="N12" s="3">
-        <v>800</v>
-      </c>
-      <c r="O12" s="3">
-        <v>200</v>
-      </c>
-      <c r="P12" s="3">
-        <v>200</v>
       </c>
       <c r="Q12" s="3">
         <v>200</v>
@@ -1207,31 +1234,31 @@
         <v>200</v>
       </c>
       <c r="T12" s="3">
+        <v>200</v>
+      </c>
+      <c r="U12" s="3">
+        <v>200</v>
+      </c>
+      <c r="V12" s="3">
         <v>300</v>
-      </c>
-      <c r="U12" s="3">
-        <v>400</v>
-      </c>
-      <c r="V12" s="3">
-        <v>200</v>
       </c>
       <c r="W12" s="3">
         <v>400</v>
       </c>
       <c r="X12" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="Y12" s="3">
         <v>400</v>
       </c>
       <c r="Z12" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AA12" s="3">
         <v>400</v>
       </c>
       <c r="AB12" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AC12" s="3">
         <v>400</v>
@@ -1240,25 +1267,31 @@
         <v>400</v>
       </c>
       <c r="AE12" s="3">
+        <v>400</v>
+      </c>
+      <c r="AF12" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG12" s="3">
         <v>200</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>500</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>600</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AJ12" s="3">
         <v>800</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AK12" s="3">
         <v>800</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AL12" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,16 +1394,22 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
+      <c r="E14" s="3">
+        <v>1700</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>4</v>
@@ -1387,66 +1426,66 @@
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>16200</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>4700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>-100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>3200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>-400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>1300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>400</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>1000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>300</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
@@ -1457,24 +1496,30 @@
         <v>0</v>
       </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>100</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
         <v>0</v>
@@ -1569,8 +1614,14 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1655,230 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F17" s="3">
         <v>2500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>2600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>4100</v>
-      </c>
-      <c r="G17" s="3">
-        <v>3200</v>
-      </c>
-      <c r="H17" s="3">
-        <v>3100</v>
       </c>
       <c r="I17" s="3">
         <v>3200</v>
       </c>
       <c r="J17" s="3">
+        <v>3100</v>
+      </c>
+      <c r="K17" s="3">
+        <v>3200</v>
+      </c>
+      <c r="L17" s="3">
         <v>5800</v>
-      </c>
-      <c r="K17" s="3">
-        <v>4700</v>
-      </c>
-      <c r="L17" s="3">
-        <v>4600</v>
       </c>
       <c r="M17" s="3">
         <v>4700</v>
       </c>
       <c r="N17" s="3">
+        <v>4600</v>
+      </c>
+      <c r="O17" s="3">
+        <v>4700</v>
+      </c>
+      <c r="P17" s="3">
         <v>4800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>20200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>3700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>3600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>15100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>5600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>4100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>3100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>2700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>2800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>3200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>1500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>2100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>2300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>1600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>1800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>2600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>2600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-2500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-4100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-3200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-3100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-3100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-5800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-4700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-4600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-4600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-4800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-20200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-3600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-15100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-5600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-1200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-4100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-1800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,41 +1915,43 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>600</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F20" s="3">
         <v>-1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>1700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-1700</v>
       </c>
-      <c r="G20" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J20" s="3">
         <v>-7800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>2700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>1400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1907,44 +1974,44 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-2100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-2100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>1100</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-100</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>200</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>0</v>
-      </c>
       <c r="AH20" s="3">
         <v>0</v>
       </c>
@@ -1954,112 +2021,124 @@
       <c r="AJ20" s="3">
         <v>0</v>
       </c>
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-4200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-2300</v>
       </c>
-      <c r="G21" s="3">
-        <v>800</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="J21" s="3">
         <v>4700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-5800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-7200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-4300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-4600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-4600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-4800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-20200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-3500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-15000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-5500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-3200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-6200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-3100</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="Z21" s="3">
-        <v>-2800</v>
       </c>
       <c r="AA21" s="3">
         <v>-2800</v>
       </c>
       <c r="AB21" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="AC21" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="AD21" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>-2500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>-2500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>-1800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2087,187 +2166,199 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
       <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
         <v>200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>200</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
-      </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
         <v>1400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>1400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>1900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>1300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>1100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>1300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>300</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>200</v>
-      </c>
-      <c r="AH22" s="3">
-        <v>200</v>
       </c>
       <c r="AI22" s="3">
         <v>200</v>
       </c>
       <c r="AJ22" s="3">
+        <v>200</v>
+      </c>
+      <c r="AK22" s="3">
+        <v>200</v>
+      </c>
+      <c r="AL22" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-4000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-2200</v>
       </c>
-      <c r="G23" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="J23" s="3">
         <v>4800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-5700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-7200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-4300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-4700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-4700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-4800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-20400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-4100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-15700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-5800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-4700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-7600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-1600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-4200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-2700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>-2100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2292,11 +2383,11 @@
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -2370,8 +2461,14 @@
       <c r="AJ24" s="3">
         <v>0</v>
       </c>
+      <c r="AK24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2571,234 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-4000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-2200</v>
       </c>
-      <c r="G26" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="J26" s="3">
         <v>4800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-5700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-7200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-4300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-4700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-4700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-4800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-20400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-4100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-15700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-5800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-4700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-7600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-1600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-4200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-2700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>-2100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-4000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-2200</v>
       </c>
-      <c r="G27" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="J27" s="3">
         <v>4800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-5700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-7200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-4300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-4700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-4700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-4800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-20400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-4100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-15700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-5800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-4700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-7600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-1600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-4200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-2700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>-2100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2901,14 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2890,8 +3011,14 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3121,14 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,41 +3231,47 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E32" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F32" s="3">
         <v>1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-1700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>1700</v>
       </c>
-      <c r="G32" s="3">
-        <v>4000</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
+        <v>500</v>
+      </c>
+      <c r="J32" s="3">
         <v>7800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-2700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-1400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -3155,44 +3294,44 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>2100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>2100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-1100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>100</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-200</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>0</v>
-      </c>
       <c r="AH32" s="3">
         <v>0</v>
       </c>
@@ -3202,112 +3341,124 @@
       <c r="AJ32" s="3">
         <v>0</v>
       </c>
+      <c r="AK32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-4000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-2200</v>
       </c>
-      <c r="G33" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="J33" s="3">
         <v>4800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-5700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-7200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-4300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-4700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-4700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-4800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-20400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-4100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-15700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-5800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-4700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-7600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-1600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-4200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-2700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>-2100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3561,239 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-4000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-2200</v>
       </c>
-      <c r="G35" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="J35" s="3">
         <v>4800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-5700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-7200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-4300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-4700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-4700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-4800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-20400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-4100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-15700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-5800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-4700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-7600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-1600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-4200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-2700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>-2100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3830,10 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,101 +3870,103 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>500</v>
+      </c>
+      <c r="F41" s="3">
         <v>1500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>2300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>6600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>17900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>19300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>21000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>2500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>3100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>300</v>
       </c>
-      <c r="V41" s="3">
-        <v>0</v>
-      </c>
-      <c r="W41" s="3">
-        <v>0</v>
-      </c>
       <c r="X41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="3">
         <v>100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>1300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>100</v>
       </c>
-      <c r="AC41" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD41" s="3">
-        <v>0</v>
-      </c>
       <c r="AE41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="3">
         <v>500</v>
       </c>
-      <c r="AF41" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG41" s="3">
-        <v>0</v>
-      </c>
       <c r="AH41" s="3">
         <v>0</v>
       </c>
@@ -3803,44 +3976,50 @@
       <c r="AJ41" s="3">
         <v>0</v>
       </c>
+      <c r="AK41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL41" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E42" s="3">
+        <v>10200</v>
+      </c>
+      <c r="F42" s="3">
         <v>11600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>12400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>15300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>10200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>9800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>9800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>10500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>13100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>9900</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3853,11 +4032,11 @@
       <c r="R42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
-      </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -3907,19 +4086,25 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
         <v>200</v>
       </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G43" s="3">
         <v>0</v>
@@ -4011,8 +4196,14 @@
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4037,11 +4228,11 @@
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4115,19 +4306,25 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>4</v>
+      <c r="F45" s="3">
+        <v>0</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>4</v>
@@ -4141,38 +4338,38 @@
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
-        <v>400</v>
-      </c>
-      <c r="L45" s="3">
-        <v>400</v>
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M45" s="3">
         <v>400</v>
       </c>
       <c r="N45" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="O45" s="3">
         <v>400</v>
       </c>
       <c r="P45" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="Q45" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="R45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S45" s="3">
         <v>100</v>
       </c>
       <c r="T45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V45" s="3">
         <v>0</v>
@@ -4181,7 +4378,7 @@
         <v>0</v>
       </c>
       <c r="X45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y45" s="3">
         <v>0</v>
@@ -4199,7 +4396,7 @@
         <v>0</v>
       </c>
       <c r="AD45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE45" s="3">
         <v>0</v>
@@ -4219,112 +4416,124 @@
       <c r="AJ45" s="3">
         <v>0</v>
       </c>
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>11100</v>
+      </c>
+      <c r="F46" s="3">
         <v>13500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>15000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>16800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>11400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>12600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>12000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>12800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>15100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>16900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>18300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>19900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>21500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>2600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>3200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>1400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>100</v>
       </c>
-      <c r="AD46" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG46" s="3">
         <v>500</v>
       </c>
-      <c r="AF46" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG46" s="3">
-        <v>0</v>
-      </c>
       <c r="AH46" s="3">
         <v>0</v>
       </c>
       <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK46" s="3">
         <v>100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4349,11 +4558,11 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4427,8 +4636,14 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4439,10 +4654,10 @@
         <v>400</v>
       </c>
       <c r="F48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="G48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H48" s="3">
         <v>500</v>
@@ -4460,79 +4675,85 @@
         <v>500</v>
       </c>
       <c r="M48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="N48" s="3">
         <v>500</v>
       </c>
       <c r="O48" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="P48" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="Q48" s="3">
         <v>400</v>
       </c>
       <c r="R48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="S48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="T48" s="3">
         <v>500</v>
       </c>
       <c r="U48" s="3">
+        <v>500</v>
+      </c>
+      <c r="V48" s="3">
+        <v>500</v>
+      </c>
+      <c r="W48" s="3">
         <v>600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>700</v>
-      </c>
-      <c r="X48" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>100</v>
       </c>
       <c r="Z48" s="3">
         <v>100</v>
       </c>
       <c r="AA48" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB48" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC48" s="3">
         <v>200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>200</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>300</v>
-      </c>
-      <c r="AD48" s="3">
-        <v>300</v>
       </c>
       <c r="AE48" s="3">
         <v>300</v>
       </c>
       <c r="AF48" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG48" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH48" s="3">
         <v>400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4540,10 +4761,10 @@
         <v>600</v>
       </c>
       <c r="E49" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="F49" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="G49" s="3">
         <v>700</v>
@@ -4552,22 +4773,22 @@
         <v>700</v>
       </c>
       <c r="I49" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="J49" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="K49" s="3">
         <v>800</v>
       </c>
       <c r="L49" s="3">
+        <v>800</v>
+      </c>
+      <c r="M49" s="3">
+        <v>800</v>
+      </c>
+      <c r="N49" s="3">
         <v>500</v>
-      </c>
-      <c r="M49" s="3">
-        <v>600</v>
-      </c>
-      <c r="N49" s="3">
-        <v>600</v>
       </c>
       <c r="O49" s="3">
         <v>600</v>
@@ -4582,10 +4803,10 @@
         <v>600</v>
       </c>
       <c r="S49" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="T49" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="U49" s="3">
         <v>700</v>
@@ -4597,10 +4818,10 @@
         <v>700</v>
       </c>
       <c r="X49" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="Y49" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="Z49" s="3">
         <v>800</v>
@@ -4612,10 +4833,10 @@
         <v>800</v>
       </c>
       <c r="AC49" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="AD49" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="AE49" s="3">
         <v>900</v>
@@ -4630,13 +4851,19 @@
         <v>900</v>
       </c>
       <c r="AI49" s="3">
+        <v>900</v>
+      </c>
+      <c r="AJ49" s="3">
+        <v>900</v>
+      </c>
+      <c r="AK49" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4966,14 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,8 +5076,14 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4875,11 +5114,11 @@
       <c r="L52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
-      <c r="N52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O52" s="3">
         <v>0</v>
@@ -4909,17 +5148,17 @@
         <v>0</v>
       </c>
       <c r="X52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="3">
         <v>400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>200</v>
       </c>
-      <c r="Z52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>0</v>
-      </c>
       <c r="AB52" s="3">
         <v>0</v>
       </c>
@@ -4933,22 +5172,28 @@
         <v>0</v>
       </c>
       <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="3">
         <v>100</v>
       </c>
-      <c r="AG52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH52" s="3">
-        <v>0</v>
-      </c>
       <c r="AI52" s="3">
         <v>0</v>
       </c>
       <c r="AJ52" s="3">
         <v>0</v>
       </c>
+      <c r="AK52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5296,124 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>12300</v>
+      </c>
+      <c r="F54" s="3">
         <v>14600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>16100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>18000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>12600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>13800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>13300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>14100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>16400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>17900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>19400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>20900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>22500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>2200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>2900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>3700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>4300</v>
-      </c>
-      <c r="T54" s="3">
-        <v>1400</v>
-      </c>
-      <c r="U54" s="3">
-        <v>1600</v>
       </c>
       <c r="V54" s="3">
         <v>1400</v>
       </c>
       <c r="W54" s="3">
+        <v>1600</v>
+      </c>
+      <c r="X54" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Y54" s="3">
         <v>1500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>2400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1600</v>
-      </c>
-      <c r="AA54" s="3">
-        <v>1200</v>
-      </c>
-      <c r="AB54" s="3">
-        <v>1300</v>
       </c>
       <c r="AC54" s="3">
         <v>1200</v>
       </c>
       <c r="AD54" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AE54" s="3">
         <v>1200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AG54" s="3">
         <v>1800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>1400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>1400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>1500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5450,10 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,19 +5490,21 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>500</v>
+      </c>
+      <c r="F57" s="3">
         <v>400</v>
-      </c>
-      <c r="E57" s="3">
-        <v>200</v>
-      </c>
-      <c r="F57" s="3">
-        <v>200</v>
       </c>
       <c r="G57" s="3">
         <v>200</v>
@@ -5252,91 +5513,97 @@
         <v>200</v>
       </c>
       <c r="I57" s="3">
+        <v>200</v>
+      </c>
+      <c r="J57" s="3">
+        <v>200</v>
+      </c>
+      <c r="K57" s="3">
         <v>300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>200</v>
-      </c>
-      <c r="O57" s="3">
-        <v>100</v>
-      </c>
-      <c r="P57" s="3">
-        <v>100</v>
       </c>
       <c r="Q57" s="3">
         <v>100</v>
       </c>
       <c r="R57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S57" s="3">
         <v>100</v>
       </c>
       <c r="T57" s="3">
+        <v>200</v>
+      </c>
+      <c r="U57" s="3">
         <v>100</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
-      </c>
       <c r="V57" s="3">
+        <v>100</v>
+      </c>
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+      <c r="X57" s="3">
         <v>2000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>2000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>1700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>1500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>1600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>1900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>2100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>2300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>2400</v>
-      </c>
-      <c r="AE57" s="3">
-        <v>2500</v>
-      </c>
-      <c r="AF57" s="3">
-        <v>2700</v>
       </c>
       <c r="AG57" s="3">
         <v>2500</v>
       </c>
       <c r="AH57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AI57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="AJ57" s="3">
         <v>2300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>2300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5344,29 +5611,29 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>100</v>
-      </c>
-      <c r="G58" s="3">
-        <v>200</v>
-      </c>
-      <c r="H58" s="3">
-        <v>200</v>
       </c>
       <c r="I58" s="3">
         <v>200</v>
       </c>
       <c r="J58" s="3">
+        <v>200</v>
+      </c>
+      <c r="K58" s="3">
+        <v>200</v>
+      </c>
+      <c r="L58" s="3">
         <v>100</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -5374,14 +5641,14 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>100</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -5389,266 +5656,284 @@
         <v>0</v>
       </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>1100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>8000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>7100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>7500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>5500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>3500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>3600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>3200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>4400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>3700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>3500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>2900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>2400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>1900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F59" s="3">
         <v>3500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>4600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1500</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M59" s="3">
         <v>300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>8300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>4600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>4400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>4100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>3600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>3700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>3700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>3900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>2700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>2400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>2500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>2100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>1800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F60" s="3">
         <v>4600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>5300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>3400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>18400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>13700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>13700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>11100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>8700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>9300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>8900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>10600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>8800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>8400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>8000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>7000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>6100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>5800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5668,17 +5953,17 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>100</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -5686,26 +5971,26 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>5800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>5000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>4700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>4300</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -5713,46 +5998,52 @@
         <v>0</v>
       </c>
       <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>1200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>400</v>
-      </c>
-      <c r="AD61" s="3">
-        <v>100</v>
-      </c>
-      <c r="AE61" s="3">
-        <v>200</v>
       </c>
       <c r="AF61" s="3">
         <v>100</v>
       </c>
       <c r="AG61" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AH61" s="3">
         <v>100</v>
       </c>
       <c r="AI61" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ61" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK61" s="3">
         <v>300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5777,66 +6068,66 @@
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
-        <v>200</v>
-      </c>
-      <c r="L62" s="3">
-        <v>200</v>
+      <c r="K62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M62" s="3">
         <v>200</v>
       </c>
       <c r="N62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="P62" s="3">
         <v>300</v>
       </c>
       <c r="Q62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="R62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="S62" s="3">
         <v>400</v>
       </c>
       <c r="T62" s="3">
+        <v>400</v>
+      </c>
+      <c r="U62" s="3">
+        <v>400</v>
+      </c>
+      <c r="V62" s="3">
         <v>15100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>15200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>500</v>
       </c>
-      <c r="X62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>0</v>
-      </c>
       <c r="Z62" s="3">
         <v>0</v>
       </c>
       <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="3">
         <v>100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>100</v>
       </c>
-      <c r="AC62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD62" s="3">
-        <v>0</v>
-      </c>
       <c r="AE62" s="3">
         <v>0</v>
       </c>
@@ -5850,13 +6141,19 @@
         <v>0</v>
       </c>
       <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK62" s="3">
         <v>400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6256,14 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6366,14 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6476,124 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F66" s="3">
         <v>4600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>5300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>3400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>2600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>900</v>
-      </c>
-      <c r="M66" s="3">
-        <v>900</v>
-      </c>
-      <c r="N66" s="3">
-        <v>800</v>
       </c>
       <c r="O66" s="3">
         <v>900</v>
       </c>
       <c r="P66" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q66" s="3">
+        <v>900</v>
+      </c>
+      <c r="R66" s="3">
         <v>7100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>6700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>6400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>5700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>16500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>16100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>18900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>14200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>13900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>11400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>9200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>9800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>10200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>11100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>8900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>8600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>8100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>7100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>6200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>6600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6630,10 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6736,14 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6846,14 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6956,14 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +7066,124 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-161000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-155700</v>
+      </c>
+      <c r="F72" s="3">
         <v>-154000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-153000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-148900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-146700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-164200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-161300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-158300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-152600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-148300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-143600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-139000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-134100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-113700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-109600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-105500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-89800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-84100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-83200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-86100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-78600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-77000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-72000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-67800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-63900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-60400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-57400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-53900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-51400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-49500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>-47500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>-44700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>-42000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>-39900</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7286,14 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7396,14 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7506,124 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>8500</v>
+      </c>
+      <c r="F76" s="3">
         <v>10000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>10800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>14500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>10000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>12800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>12400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>13500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>15800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>17000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>18600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>20100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>21600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>-3800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>-2700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>-1300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>-15100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>-14400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>-17500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>-12800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>-12400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>-8900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>-8600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>-8900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>-9900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>-7700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>-6800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>-6700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>-5700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>-4700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>-5000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7726,239 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-4000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-2200</v>
       </c>
-      <c r="G81" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="J81" s="3">
         <v>4800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-5700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-7200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-4300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-4700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-4700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-4800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-20400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-4100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-15700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-5800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-4700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-7600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-1600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-4200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-2700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>-2100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,8 +7995,10 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7657,7 +8054,7 @@
         <v>0</v>
       </c>
       <c r="U83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
@@ -7666,7 +8063,7 @@
         <v>100</v>
       </c>
       <c r="X83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y83" s="3">
         <v>100</v>
@@ -7704,8 +8101,14 @@
       <c r="AJ83" s="3">
         <v>100</v>
       </c>
+      <c r="AK83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL83" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8211,14 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8321,14 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8431,14 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8541,14 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8651,124 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-2300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K89" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="L89" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="M89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="N89" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="O89" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="P89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="R89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="S89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="T89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="U89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="V89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="W89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="X89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-1800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="Z89" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="AA89" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="AB89" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="AC89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AD89" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="AE89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AF89" s="3">
         <v>-1200</v>
       </c>
-      <c r="I89" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="N89" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="O89" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-600</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>-700</v>
-      </c>
-      <c r="R89" s="3">
+      <c r="AG89" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="AH89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AI89" s="3">
         <v>-800</v>
-      </c>
-      <c r="S89" s="3">
-        <v>-600</v>
-      </c>
-      <c r="T89" s="3">
-        <v>-500</v>
-      </c>
-      <c r="U89" s="3">
-        <v>-900</v>
-      </c>
-      <c r="V89" s="3">
-        <v>-400</v>
-      </c>
-      <c r="W89" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="X89" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="AA89" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="AB89" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="AC89" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="AD89" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="AE89" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="AF89" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AG89" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AH89" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="AI89" s="3">
-        <v>-1100</v>
       </c>
       <c r="AJ89" s="3">
         <v>-1200</v>
       </c>
+      <c r="AK89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AL89" s="3">
+        <v>-1200</v>
+      </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,31 +8805,33 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -8399,31 +8840,31 @@
         <v>-100</v>
       </c>
       <c r="M91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N91" s="3">
         <v>-100</v>
       </c>
       <c r="O91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>4</v>
+        <v>-100</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="T91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -8434,23 +8875,23 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD91" s="3" t="s">
-        <v>4</v>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
+        <v>0</v>
       </c>
       <c r="AE91" s="3" t="s">
         <v>4</v>
@@ -8464,14 +8905,20 @@
       <c r="AH91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ91" s="3">
+      <c r="AI91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL91" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +9021,14 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,50 +9131,56 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E94" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F94" s="3">
         <v>900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>3000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-4900</v>
       </c>
-      <c r="G94" s="3">
-        <v>100</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>2500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-3200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-9900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>4</v>
       </c>
@@ -8731,11 +9190,11 @@
       <c r="S94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="T94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
@@ -8746,29 +9205,29 @@
       <c r="X94" s="3">
         <v>0</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF94" s="3">
-        <v>0</v>
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG94" s="3">
         <v>0</v>
@@ -8782,8 +9241,14 @@
       <c r="AJ94" s="3">
         <v>0</v>
       </c>
+      <c r="AK94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9285,10 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8846,11 +9313,11 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -8924,8 +9391,14 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9501,14 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9611,14 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,37 +9721,43 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>7500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>1900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>400</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
@@ -9275,73 +9766,79 @@
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>21100</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>3500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>1200</v>
-      </c>
-      <c r="V100" s="3">
-        <v>500</v>
-      </c>
-      <c r="W100" s="3">
-        <v>1700</v>
       </c>
       <c r="X100" s="3">
         <v>500</v>
       </c>
       <c r="Y100" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Z100" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA100" s="3">
         <v>2200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>2400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>1600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>1500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>1000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>1800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>1200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9366,11 +9863,11 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9444,101 +9941,107 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F102" s="3">
         <v>-800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>1100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-1600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-4900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-11400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-1400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-1700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>19900</v>
-      </c>
-      <c r="P102" s="3">
-        <v>-600</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>-700</v>
       </c>
       <c r="R102" s="3">
         <v>-600</v>
       </c>
       <c r="S102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="T102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="U102" s="3">
         <v>2900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>300</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>400</v>
       </c>
-      <c r="AA102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
         <v>100</v>
       </c>
-      <c r="AC102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
         <v>-400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>500</v>
       </c>
-      <c r="AF102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG102" s="3">
-        <v>0</v>
-      </c>
       <c r="AH102" s="3">
         <v>0</v>
       </c>
@@ -9546,6 +10049,12 @@
         <v>0</v>
       </c>
       <c r="AJ102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL102" s="3">
         <v>-500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BRTX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BRTX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="92">
   <si>
     <t>BRTX</t>
   </si>
@@ -656,180 +656,184 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>4</v>
+      <c r="D8" s="3">
+        <v>300</v>
       </c>
       <c r="E8" s="3">
         <v>0</v>
       </c>
       <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
         <v>200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>100</v>
       </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
       <c r="I8" s="3">
         <v>0</v>
       </c>
@@ -837,11 +841,11 @@
         <v>0</v>
       </c>
       <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
         <v>100</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
       <c r="M8" s="3">
         <v>0</v>
       </c>
@@ -849,11 +853,11 @@
         <v>0</v>
       </c>
       <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
         <v>100</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
       <c r="Q8" s="3">
         <v>0</v>
       </c>
@@ -920,8 +924,11 @@
       <c r="AL8" s="3">
         <v>0</v>
       </c>
+      <c r="AM8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -937,8 +944,8 @@
       <c r="G9" s="3">
         <v>0</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>4</v>
+      <c r="H9" s="3">
+        <v>0</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>4</v>
@@ -1024,32 +1031,35 @@
       <c r="AJ9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK9" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL9" s="3" t="s">
+      <c r="AK9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E10" s="3">
         <v>0</v>
       </c>
       <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
         <v>200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>100</v>
       </c>
-      <c r="H10" s="3">
-        <v>0</v>
-      </c>
       <c r="I10" s="3">
         <v>0</v>
       </c>
@@ -1057,13 +1067,13 @@
         <v>0</v>
       </c>
       <c r="K10" s="3">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
         <v>100</v>
       </c>
-      <c r="L10" s="3">
-        <v>0</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>4</v>
+      <c r="M10" s="3">
+        <v>0</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>4</v>
@@ -1134,14 +1144,17 @@
       <c r="AJ10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL10" s="3" t="s">
+      <c r="AK10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM10" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1180,52 +1193,53 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1700</v>
+        <v>2200</v>
       </c>
       <c r="E12" s="3">
         <v>1700</v>
       </c>
       <c r="F12" s="3">
-        <v>1300</v>
+        <v>1700</v>
       </c>
       <c r="G12" s="3">
         <v>1300</v>
       </c>
       <c r="H12" s="3">
-        <v>1100</v>
+        <v>1500</v>
       </c>
       <c r="I12" s="3">
         <v>1100</v>
       </c>
       <c r="J12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K12" s="3">
         <v>800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>800</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>200</v>
       </c>
       <c r="R12" s="3">
         <v>200</v>
@@ -1240,16 +1254,16 @@
         <v>200</v>
       </c>
       <c r="V12" s="3">
+        <v>200</v>
+      </c>
+      <c r="W12" s="3">
         <v>300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>200</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>400</v>
       </c>
       <c r="Z12" s="3">
         <v>400</v>
@@ -1258,10 +1272,10 @@
         <v>400</v>
       </c>
       <c r="AB12" s="3">
+        <v>400</v>
+      </c>
+      <c r="AC12" s="3">
         <v>500</v>
-      </c>
-      <c r="AC12" s="3">
-        <v>400</v>
       </c>
       <c r="AD12" s="3">
         <v>400</v>
@@ -1273,25 +1287,28 @@
         <v>400</v>
       </c>
       <c r="AG12" s="3">
+        <v>400</v>
+      </c>
+      <c r="AH12" s="3">
         <v>200</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>500</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>600</v>
-      </c>
-      <c r="AJ12" s="3">
-        <v>800</v>
       </c>
       <c r="AK12" s="3">
         <v>800</v>
       </c>
       <c r="AL12" s="3">
+        <v>800</v>
+      </c>
+      <c r="AM12" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,20 +1417,23 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
         <v>1700</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1432,8 +1452,8 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1442,14 +1462,14 @@
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>16200</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
@@ -1457,38 +1477,38 @@
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>4700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>3200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1300</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>400</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>300</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
@@ -1502,16 +1522,19 @@
         <v>0</v>
       </c>
       <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
         <v>100</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1522,7 +1545,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
         <v>0</v>
@@ -1620,8 +1643,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E17" s="3">
         <v>4800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>20200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>15100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1800</v>
-      </c>
-      <c r="AI17" s="3">
-        <v>2600</v>
       </c>
       <c r="AJ17" s="3">
         <v>2600</v>
       </c>
       <c r="AK17" s="3">
+        <v>2600</v>
+      </c>
+      <c r="AL17" s="3">
         <v>1900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-4800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-4100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3200</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-3100</v>
       </c>
       <c r="K18" s="3">
         <v>-3100</v>
       </c>
       <c r="L18" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="M18" s="3">
         <v>-5800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4700</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-4600</v>
       </c>
       <c r="O18" s="3">
         <v>-4600</v>
       </c>
       <c r="P18" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-20200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-15100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-5600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-1800</v>
-      </c>
-      <c r="AI18" s="3">
-        <v>-2600</v>
       </c>
       <c r="AJ18" s="3">
         <v>-2600</v>
       </c>
       <c r="AK18" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="AL18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,44 +1950,45 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E20" s="3">
         <v>600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-7800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>300</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1980,40 +2014,40 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
-        <v>-2100</v>
+        <v>0</v>
       </c>
       <c r="X20" s="3">
         <v>-2100</v>
       </c>
       <c r="Y20" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="Z20" s="3">
         <v>1100</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-100</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>200</v>
       </c>
       <c r="AG20" s="3">
         <v>200</v>
       </c>
       <c r="AH20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AI20" s="3">
         <v>0</v>
@@ -2027,82 +2061,85 @@
       <c r="AL20" s="3">
         <v>0</v>
       </c>
+      <c r="AM20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-5400</v>
       </c>
-      <c r="E21" s="3">
-        <v>0</v>
-      </c>
       <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
         <v>-1200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-4200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-5800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-7200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-4300</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-4600</v>
       </c>
       <c r="O21" s="3">
         <v>-4600</v>
       </c>
       <c r="P21" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-20200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-3700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-3500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-15000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-5500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-3200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-6200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-3100</v>
-      </c>
-      <c r="AA21" s="3">
-        <v>-2800</v>
       </c>
       <c r="AB21" s="3">
         <v>-2800</v>
@@ -2111,34 +2148,37 @@
         <v>-2800</v>
       </c>
       <c r="AD21" s="3">
-        <v>-2100</v>
+        <v>-2800</v>
       </c>
       <c r="AE21" s="3">
         <v>-2100</v>
       </c>
       <c r="AF21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="AG21" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-1700</v>
-      </c>
-      <c r="AI21" s="3">
-        <v>-2500</v>
       </c>
       <c r="AJ21" s="3">
         <v>-2500</v>
       </c>
       <c r="AK21" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="AL21" s="3">
         <v>-1800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2172,8 +2212,8 @@
       <c r="M22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -2182,61 +2222,61 @@
         <v>0</v>
       </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>200</v>
-      </c>
-      <c r="R22" s="3">
-        <v>500</v>
       </c>
       <c r="S22" s="3">
         <v>500</v>
       </c>
       <c r="T22" s="3">
+        <v>500</v>
+      </c>
+      <c r="U22" s="3">
         <v>600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>200</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
       <c r="W22" s="3">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="X22" s="3">
         <v>1400</v>
       </c>
       <c r="Y22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Z22" s="3">
         <v>900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1300</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>400</v>
       </c>
       <c r="AG22" s="3">
         <v>400</v>
       </c>
       <c r="AH22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AI22" s="3">
         <v>300</v>
-      </c>
-      <c r="AI22" s="3">
-        <v>200</v>
       </c>
       <c r="AJ22" s="3">
         <v>200</v>
@@ -2245,120 +2285,126 @@
         <v>200</v>
       </c>
       <c r="AL22" s="3">
+        <v>200</v>
+      </c>
+      <c r="AM22" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4300</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-4700</v>
       </c>
       <c r="O23" s="3">
         <v>-4700</v>
       </c>
       <c r="P23" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-20400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-4100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-15700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-5800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-4700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-7600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-4200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-2500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-2100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-2700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-2100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2389,8 +2435,8 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -2467,8 +2513,11 @@
       <c r="AL24" s="3">
         <v>0</v>
       </c>
+      <c r="AM24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4300</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-4700</v>
       </c>
       <c r="O26" s="3">
         <v>-4700</v>
       </c>
       <c r="P26" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-20400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-15700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-5800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-4700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-7600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-4200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-2500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-2100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-2700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-2100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4300</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-4700</v>
       </c>
       <c r="O27" s="3">
         <v>-4700</v>
       </c>
       <c r="P27" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-20400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-15700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-5800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-4700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-7600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-4200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-2500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-2100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-2700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-2100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,44 +3304,47 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>7800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-300</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -3300,40 +3370,40 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="X32" s="3">
         <v>2100</v>
       </c>
       <c r="Y32" s="3">
+        <v>2100</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>100</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>100</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>-200</v>
       </c>
       <c r="AG32" s="3">
         <v>-200</v>
       </c>
       <c r="AH32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="AI32" s="3">
         <v>0</v>
@@ -3347,118 +3417,124 @@
       <c r="AL32" s="3">
         <v>0</v>
       </c>
+      <c r="AM32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-4300</v>
-      </c>
-      <c r="N33" s="3">
-        <v>-4700</v>
       </c>
       <c r="O33" s="3">
         <v>-4700</v>
       </c>
       <c r="P33" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-20400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-15700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-5800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-4700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-7600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-4200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-2100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-2700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-2100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-4300</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-4700</v>
       </c>
       <c r="O35" s="3">
         <v>-4700</v>
       </c>
       <c r="P35" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-20400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-15700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-5800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-4700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-7600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-4200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-2100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-2700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-2100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,104 +3958,105 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E41" s="3">
         <v>1200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2400</v>
-      </c>
-      <c r="K41" s="3">
-        <v>1800</v>
       </c>
       <c r="L41" s="3">
         <v>1800</v>
       </c>
       <c r="M41" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N41" s="3">
         <v>1700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>17900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>19300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>21000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>300</v>
       </c>
-      <c r="X41" s="3">
-        <v>0</v>
-      </c>
       <c r="Y41" s="3">
         <v>0</v>
       </c>
       <c r="Z41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="3">
         <v>100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>500</v>
-      </c>
-      <c r="AC41" s="3">
-        <v>100</v>
       </c>
       <c r="AD41" s="3">
         <v>100</v>
       </c>
       <c r="AE41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF41" s="3">
         <v>0</v>
       </c>
       <c r="AG41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH41" s="3">
         <v>500</v>
       </c>
-      <c r="AH41" s="3">
-        <v>0</v>
-      </c>
       <c r="AI41" s="3">
         <v>0</v>
       </c>
@@ -3982,47 +4069,50 @@
       <c r="AL41" s="3">
         <v>0</v>
       </c>
+      <c r="AM41" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E42" s="3">
         <v>7900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>10200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>11600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>12400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>15300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>10200</v>
-      </c>
-      <c r="J42" s="3">
-        <v>9800</v>
       </c>
       <c r="K42" s="3">
         <v>9800</v>
       </c>
       <c r="L42" s="3">
+        <v>9800</v>
+      </c>
+      <c r="M42" s="3">
         <v>10500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>13100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>9900</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>4</v>
       </c>
@@ -4038,8 +4128,8 @@
       <c r="T42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -4092,8 +4182,11 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4101,13 +4194,13 @@
         <v>0</v>
       </c>
       <c r="E43" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F43" s="3">
         <v>200</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H43" s="3">
         <v>0</v>
@@ -4202,8 +4295,11 @@
       <c r="AL43" s="3">
         <v>0</v>
       </c>
+      <c r="AM43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4234,8 +4330,8 @@
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4312,22 +4408,25 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>4</v>
+      <c r="D45" s="3">
+        <v>0</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>4</v>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3">
+        <v>0</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>4</v>
@@ -4344,8 +4443,8 @@
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="3">
-        <v>400</v>
+      <c r="M45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N45" s="3">
         <v>400</v>
@@ -4354,16 +4453,16 @@
         <v>400</v>
       </c>
       <c r="P45" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q45" s="3">
         <v>500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>400</v>
       </c>
-      <c r="R45" s="3">
-        <v>0</v>
-      </c>
       <c r="S45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T45" s="3">
         <v>100</v>
@@ -4372,7 +4471,7 @@
         <v>100</v>
       </c>
       <c r="V45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W45" s="3">
         <v>0</v>
@@ -4384,23 +4483,23 @@
         <v>0</v>
       </c>
       <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="3">
         <v>100</v>
       </c>
-      <c r="AA45" s="3">
-        <v>0</v>
-      </c>
       <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="3">
         <v>100</v>
       </c>
-      <c r="AC45" s="3">
-        <v>0</v>
-      </c>
       <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="3">
         <v>100</v>
       </c>
-      <c r="AE45" s="3">
-        <v>0</v>
-      </c>
       <c r="AF45" s="3">
         <v>0</v>
       </c>
@@ -4422,104 +4521,107 @@
       <c r="AL45" s="3">
         <v>0</v>
       </c>
+      <c r="AM45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E46" s="3">
         <v>9400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>11100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>13500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>15000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>15100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>16900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>18300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>19900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>21500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>300</v>
-      </c>
-      <c r="X46" s="3">
-        <v>100</v>
       </c>
       <c r="Y46" s="3">
         <v>100</v>
       </c>
       <c r="Z46" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA46" s="3">
         <v>200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>600</v>
-      </c>
-      <c r="AC46" s="3">
-        <v>200</v>
       </c>
       <c r="AD46" s="3">
         <v>200</v>
       </c>
       <c r="AE46" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF46" s="3">
         <v>100</v>
       </c>
-      <c r="AF46" s="3">
-        <v>0</v>
-      </c>
       <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="3">
         <v>500</v>
       </c>
-      <c r="AH46" s="3">
-        <v>0</v>
-      </c>
       <c r="AI46" s="3">
         <v>0</v>
       </c>
@@ -4527,13 +4629,16 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL46" s="3">
         <v>100</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4564,8 +4669,8 @@
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4642,13 +4747,16 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E48" s="3">
         <v>400</v>
@@ -4660,7 +4768,7 @@
         <v>400</v>
       </c>
       <c r="H48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I48" s="3">
         <v>500</v>
@@ -4681,13 +4789,13 @@
         <v>500</v>
       </c>
       <c r="O48" s="3">
+        <v>500</v>
+      </c>
+      <c r="P48" s="3">
         <v>600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>500</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>400</v>
       </c>
       <c r="R48" s="3">
         <v>400</v>
@@ -4696,7 +4804,7 @@
         <v>400</v>
       </c>
       <c r="T48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="U48" s="3">
         <v>500</v>
@@ -4705,16 +4813,16 @@
         <v>500</v>
       </c>
       <c r="W48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="X48" s="3">
         <v>600</v>
       </c>
       <c r="Y48" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z48" s="3">
         <v>700</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>100</v>
       </c>
       <c r="AA48" s="3">
         <v>100</v>
@@ -4723,13 +4831,13 @@
         <v>100</v>
       </c>
       <c r="AC48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AD48" s="3">
         <v>200</v>
       </c>
       <c r="AE48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AF48" s="3">
         <v>300</v>
@@ -4738,22 +4846,25 @@
         <v>300</v>
       </c>
       <c r="AH48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AI48" s="3">
         <v>400</v>
       </c>
       <c r="AJ48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AK48" s="3">
         <v>500</v>
       </c>
       <c r="AL48" s="3">
+        <v>500</v>
+      </c>
+      <c r="AM48" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4767,7 +4878,7 @@
         <v>600</v>
       </c>
       <c r="G49" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="H49" s="3">
         <v>700</v>
@@ -4779,7 +4890,7 @@
         <v>700</v>
       </c>
       <c r="K49" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="L49" s="3">
         <v>800</v>
@@ -4788,10 +4899,10 @@
         <v>800</v>
       </c>
       <c r="N49" s="3">
+        <v>800</v>
+      </c>
+      <c r="O49" s="3">
         <v>500</v>
-      </c>
-      <c r="O49" s="3">
-        <v>600</v>
       </c>
       <c r="P49" s="3">
         <v>600</v>
@@ -4809,7 +4920,7 @@
         <v>600</v>
       </c>
       <c r="U49" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="V49" s="3">
         <v>700</v>
@@ -4824,7 +4935,7 @@
         <v>700</v>
       </c>
       <c r="Z49" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="AA49" s="3">
         <v>800</v>
@@ -4839,7 +4950,7 @@
         <v>800</v>
       </c>
       <c r="AE49" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="AF49" s="3">
         <v>900</v>
@@ -4857,13 +4968,16 @@
         <v>900</v>
       </c>
       <c r="AK49" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AL49" s="3">
         <v>1000</v>
       </c>
+      <c r="AM49" s="3">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,8 +5199,11 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5120,8 +5240,8 @@
       <c r="N52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
@@ -5154,14 +5274,14 @@
         <v>0</v>
       </c>
       <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="3">
         <v>400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>200</v>
       </c>
-      <c r="AB52" s="3">
-        <v>0</v>
-      </c>
       <c r="AC52" s="3">
         <v>0</v>
       </c>
@@ -5178,11 +5298,11 @@
         <v>0</v>
       </c>
       <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI52" s="3">
         <v>100</v>
       </c>
-      <c r="AI52" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ52" s="3">
         <v>0</v>
       </c>
@@ -5192,8 +5312,11 @@
       <c r="AL52" s="3">
         <v>0</v>
       </c>
+      <c r="AM52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E54" s="3">
         <v>10300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>14600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>16100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>18000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>13800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>13300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>16400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>17900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>19400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>20900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>22500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1400</v>
-      </c>
-      <c r="Y54" s="3">
-        <v>1500</v>
       </c>
       <c r="Z54" s="3">
         <v>1500</v>
       </c>
       <c r="AA54" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AB54" s="3">
         <v>2400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1300</v>
-      </c>
-      <c r="AE54" s="3">
-        <v>1200</v>
       </c>
       <c r="AF54" s="3">
         <v>1200</v>
       </c>
       <c r="AG54" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AH54" s="3">
         <v>1800</v>
-      </c>
-      <c r="AH54" s="3">
-        <v>1400</v>
       </c>
       <c r="AI54" s="3">
         <v>1400</v>
       </c>
       <c r="AJ54" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AK54" s="3">
         <v>1500</v>
-      </c>
-      <c r="AK54" s="3">
-        <v>1600</v>
       </c>
       <c r="AL54" s="3">
         <v>1600</v>
       </c>
+      <c r="AM54" s="3">
+        <v>1600</v>
+      </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,8 +5622,9 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5501,13 +5632,13 @@
         <v>600</v>
       </c>
       <c r="E57" s="3">
+        <v>600</v>
+      </c>
+      <c r="F57" s="3">
         <v>500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>400</v>
-      </c>
-      <c r="G57" s="3">
-        <v>200</v>
       </c>
       <c r="H57" s="3">
         <v>200</v>
@@ -5519,25 +5650,25 @@
         <v>200</v>
       </c>
       <c r="K57" s="3">
+        <v>200</v>
+      </c>
+      <c r="L57" s="3">
         <v>300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>200</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>100</v>
       </c>
       <c r="R57" s="3">
         <v>100</v>
@@ -5546,64 +5677,67 @@
         <v>100</v>
       </c>
       <c r="T57" s="3">
+        <v>100</v>
+      </c>
+      <c r="U57" s="3">
         <v>200</v>
-      </c>
-      <c r="U57" s="3">
-        <v>100</v>
       </c>
       <c r="V57" s="3">
         <v>100</v>
       </c>
       <c r="W57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X57" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Y57" s="3">
         <v>2000</v>
       </c>
       <c r="Z57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AA57" s="3">
         <v>1700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2500</v>
-      </c>
-      <c r="AJ57" s="3">
-        <v>2300</v>
       </c>
       <c r="AK57" s="3">
         <v>2300</v>
       </c>
       <c r="AL57" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AM57" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5617,13 +5751,13 @@
         <v>0</v>
       </c>
       <c r="G58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3">
         <v>100</v>
       </c>
       <c r="I58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J58" s="3">
         <v>200</v>
@@ -5632,11 +5766,11 @@
         <v>200</v>
       </c>
       <c r="L58" s="3">
+        <v>200</v>
+      </c>
+      <c r="M58" s="3">
         <v>100</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -5647,11 +5781,11 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>100</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
       <c r="S58" s="3">
         <v>0</v>
       </c>
@@ -5662,278 +5796,287 @@
         <v>0</v>
       </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>1100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>8000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>7100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>7500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>5500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>4400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>2900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>2400</v>
-      </c>
-      <c r="AJ58" s="3">
-        <v>1900</v>
       </c>
       <c r="AK58" s="3">
         <v>1900</v>
       </c>
       <c r="AL58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AM58" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E59" s="3">
         <v>3300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1500</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N59" s="3">
         <v>300</v>
-      </c>
-      <c r="N59" s="3">
-        <v>200</v>
       </c>
       <c r="O59" s="3">
         <v>200</v>
       </c>
       <c r="P59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q59" s="3">
         <v>300</v>
       </c>
       <c r="R59" s="3">
+        <v>300</v>
+      </c>
+      <c r="S59" s="3">
         <v>700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>8300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3600</v>
-      </c>
-      <c r="AC59" s="3">
-        <v>3700</v>
       </c>
       <c r="AD59" s="3">
         <v>3700</v>
       </c>
       <c r="AE59" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AF59" s="3">
         <v>3900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E60" s="3">
         <v>4200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>900</v>
-      </c>
-      <c r="S60" s="3">
-        <v>1300</v>
       </c>
       <c r="T60" s="3">
         <v>1300</v>
       </c>
       <c r="U60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="V60" s="3">
         <v>1000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>18400</v>
-      </c>
-      <c r="Y60" s="3">
-        <v>13700</v>
       </c>
       <c r="Z60" s="3">
         <v>13700</v>
       </c>
       <c r="AA60" s="3">
+        <v>13700</v>
+      </c>
+      <c r="AB60" s="3">
         <v>11100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>8700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>9300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>8900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>10600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>8800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>8400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>8000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>7000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>6100</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>5800</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5959,13 +6102,13 @@
         <v>0</v>
       </c>
       <c r="K61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L61" s="3">
         <v>100</v>
       </c>
       <c r="M61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N61" s="3">
         <v>0</v>
@@ -5977,23 +6120,23 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4300</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -6004,31 +6147,31 @@
         <v>0</v>
       </c>
       <c r="Z61" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AA61" s="3">
         <v>200</v>
       </c>
       <c r="AB61" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AC61" s="3">
         <v>500</v>
       </c>
       <c r="AD61" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE61" s="3">
         <v>1200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>200</v>
-      </c>
-      <c r="AH61" s="3">
-        <v>100</v>
       </c>
       <c r="AI61" s="3">
         <v>100</v>
@@ -6037,13 +6180,16 @@
         <v>100</v>
       </c>
       <c r="AK61" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL61" s="3">
         <v>300</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6074,8 +6220,8 @@
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M62" s="3">
-        <v>200</v>
+      <c r="M62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N62" s="3">
         <v>200</v>
@@ -6084,7 +6230,7 @@
         <v>200</v>
       </c>
       <c r="P62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q62" s="3">
         <v>300</v>
@@ -6093,7 +6239,7 @@
         <v>300</v>
       </c>
       <c r="S62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="T62" s="3">
         <v>400</v>
@@ -6102,19 +6248,19 @@
         <v>400</v>
       </c>
       <c r="V62" s="3">
+        <v>400</v>
+      </c>
+      <c r="W62" s="3">
         <v>15100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>15200</v>
-      </c>
-      <c r="X62" s="3">
-        <v>500</v>
       </c>
       <c r="Y62" s="3">
         <v>500</v>
       </c>
       <c r="Z62" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AA62" s="3">
         <v>0</v>
@@ -6123,13 +6269,13 @@
         <v>0</v>
       </c>
       <c r="AC62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD62" s="3">
         <v>100</v>
       </c>
       <c r="AE62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF62" s="3">
         <v>0</v>
@@ -6147,13 +6293,16 @@
         <v>0</v>
       </c>
       <c r="AK62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL62" s="3">
         <v>400</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E66" s="3">
         <v>4200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>900</v>
-      </c>
-      <c r="L66" s="3">
-        <v>600</v>
       </c>
       <c r="M66" s="3">
         <v>600</v>
       </c>
       <c r="N66" s="3">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="O66" s="3">
         <v>900</v>
       </c>
       <c r="P66" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q66" s="3">
         <v>800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>6700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>6400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>16500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>16100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>18900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>14200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>13900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>11400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>9200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>9800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>10200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>11100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>8900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>8600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>8100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>7100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>6200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>6600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-163700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-161000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-155700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-154000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-153000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-148900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-146700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-164200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-161300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-158300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-152600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-148300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-143600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-139000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-134100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-113700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-109600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-105500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-89800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-84100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-83200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-86100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-78600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-77000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-72000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-67800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-63900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-60400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-57400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-53900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-51400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-49500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-47500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-44700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-42000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-39900</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E76" s="3">
         <v>6100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>14500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>15800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>17000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>18600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>20100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>21600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-4900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-3800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-2700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-1300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-15100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-14400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-17500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-12800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-12400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-8900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-7700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-8600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-8900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-9900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-7700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-6800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-6700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>-5700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>-4700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>-5000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-4300</v>
-      </c>
-      <c r="N81" s="3">
-        <v>-4700</v>
       </c>
       <c r="O81" s="3">
         <v>-4700</v>
       </c>
       <c r="P81" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-20400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-15700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-5800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-4700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-7600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-4200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-2100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-2700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-2100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,8 +8195,9 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8060,13 +8259,13 @@
         <v>0</v>
       </c>
       <c r="W83" s="3">
+        <v>0</v>
+      </c>
+      <c r="X83" s="3">
         <v>100</v>
       </c>
-      <c r="X83" s="3">
-        <v>0</v>
-      </c>
       <c r="Y83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z83" s="3">
         <v>100</v>
@@ -8107,8 +8306,11 @@
       <c r="AL83" s="3">
         <v>100</v>
       </c>
+      <c r="AM83" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,8 +9027,9 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8819,31 +9040,31 @@
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I91" s="3">
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O91" s="3">
         <v>-100</v>
@@ -8852,13 +9073,13 @@
         <v>-100</v>
       </c>
       <c r="Q91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>4</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>4</v>
@@ -8866,8 +9087,8 @@
       <c r="U91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
@@ -8881,20 +9102,20 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>4</v>
+      <c r="AA91" s="3">
+        <v>0</v>
       </c>
       <c r="AB91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
+      <c r="AC91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>4</v>
+      <c r="AE91" s="3">
+        <v>0</v>
       </c>
       <c r="AF91" s="3" t="s">
         <v>4</v>
@@ -8911,14 +9132,17 @@
       <c r="AJ91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK91" s="3">
-        <v>0</v>
+      <c r="AK91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AL91" s="3">
         <v>0</v>
       </c>
+      <c r="AM91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,52 +9364,55 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E94" s="3">
         <v>2400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>3000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>2500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9900</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-100</v>
       </c>
       <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>4</v>
+      <c r="Q94" s="3">
+        <v>-100</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>4</v>
@@ -9196,8 +9426,8 @@
       <c r="U94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
@@ -9211,26 +9441,26 @@
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>4</v>
+      <c r="AA94" s="3">
+        <v>0</v>
       </c>
       <c r="AB94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
+      <c r="AC94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD94" s="3">
         <v>0</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>4</v>
+      <c r="AE94" s="3">
+        <v>0</v>
       </c>
       <c r="AF94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG94" s="3">
-        <v>0</v>
+      <c r="AG94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH94" s="3">
         <v>0</v>
@@ -9247,8 +9477,11 @@
       <c r="AL94" s="3">
         <v>0</v>
       </c>
+      <c r="AM94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,8 +9520,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9319,8 +9553,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9397,8 +9631,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,40 +9970,43 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>900</v>
+      </c>
+      <c r="E100" s="3">
         <v>1100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>7500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>400</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -9772,73 +10018,76 @@
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>21100</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>3500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>1200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>1100</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9869,8 +10118,8 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9947,104 +10196,107 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>300</v>
+      </c>
+      <c r="E102" s="3">
         <v>700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-11400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>19900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>300</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
       <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>400</v>
       </c>
-      <c r="AC102" s="3">
-        <v>0</v>
-      </c>
       <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3">
         <v>100</v>
       </c>
-      <c r="AE102" s="3">
-        <v>0</v>
-      </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>-400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>500</v>
       </c>
-      <c r="AH102" s="3">
-        <v>0</v>
-      </c>
       <c r="AI102" s="3">
         <v>0</v>
       </c>
@@ -10055,6 +10307,9 @@
         <v>0</v>
       </c>
       <c r="AL102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="3">
         <v>-500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BRTX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BRTX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="92">
   <si>
     <t>BRTX</t>
   </si>
@@ -656,170 +656,177 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -827,50 +834,50 @@
         <v>4</v>
       </c>
       <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
         <v>300</v>
       </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
       <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
         <v>200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>100</v>
       </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
       <c r="L8" s="3">
         <v>0</v>
       </c>
       <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
         <v>100</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
       <c r="P8" s="3">
         <v>0</v>
       </c>
       <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3">
         <v>100</v>
       </c>
-      <c r="R8" s="3">
-        <v>0</v>
-      </c>
-      <c r="S8" s="3">
-        <v>0</v>
-      </c>
       <c r="T8" s="3">
         <v>0</v>
       </c>
@@ -934,8 +941,14 @@
       <c r="AN8" s="3">
         <v>0</v>
       </c>
+      <c r="AO8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -957,11 +970,11 @@
       <c r="I9" s="3">
         <v>0</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>4</v>
+      <c r="J9" s="3">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3">
+        <v>0</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>4</v>
@@ -1044,14 +1057,20 @@
       <c r="AL9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AM9" s="3">
-        <v>0</v>
+      <c r="AM9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AN9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AO9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1059,40 +1078,40 @@
         <v>0</v>
       </c>
       <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
         <v>300</v>
       </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
-      <c r="G10" s="3">
-        <v>0</v>
-      </c>
       <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
         <v>200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>100</v>
       </c>
-      <c r="J10" s="3">
-        <v>0</v>
-      </c>
-      <c r="K10" s="3">
-        <v>0</v>
-      </c>
       <c r="L10" s="3">
         <v>0</v>
       </c>
       <c r="M10" s="3">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3">
         <v>100</v>
       </c>
-      <c r="N10" s="3">
-        <v>0</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>4</v>
+      <c r="P10" s="3">
+        <v>0</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>4</v>
@@ -1160,14 +1179,20 @@
       <c r="AL10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AM10" s="3">
-        <v>0</v>
+      <c r="AM10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AN10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AO10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1208,61 +1233,63 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E12" s="3">
         <v>2600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
+        <v>2600</v>
+      </c>
+      <c r="G12" s="3">
         <v>2200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>1700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>1700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>1500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>1500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>1100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>1100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>1200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>1000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>1100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>800</v>
-      </c>
-      <c r="S12" s="3">
-        <v>200</v>
-      </c>
-      <c r="T12" s="3">
-        <v>200</v>
       </c>
       <c r="U12" s="3">
         <v>200</v>
@@ -1274,31 +1301,31 @@
         <v>200</v>
       </c>
       <c r="X12" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z12" s="3">
         <v>300</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>400</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>200</v>
       </c>
       <c r="AA12" s="3">
         <v>400</v>
       </c>
       <c r="AB12" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="AC12" s="3">
         <v>400</v>
       </c>
       <c r="AD12" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AE12" s="3">
         <v>400</v>
       </c>
       <c r="AF12" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AG12" s="3">
         <v>400</v>
@@ -1307,25 +1334,31 @@
         <v>400</v>
       </c>
       <c r="AI12" s="3">
+        <v>400</v>
+      </c>
+      <c r="AJ12" s="3">
+        <v>400</v>
+      </c>
+      <c r="AK12" s="3">
         <v>200</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AL12" s="3">
         <v>500</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AM12" s="3">
         <v>600</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AN12" s="3">
         <v>800</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AO12" s="3">
         <v>800</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AP12" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1440,8 +1473,14 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1454,15 +1493,15 @@
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3">
         <v>1700</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1478,66 +1517,66 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>-300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>16200</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>4700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>-100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>3200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>-400</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>1300</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>600</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AF14" s="3">
         <v>400</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AG14" s="3">
         <v>1000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AH14" s="3">
         <v>300</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
       <c r="AI14" s="3">
         <v>0</v>
       </c>
@@ -1548,16 +1587,22 @@
         <v>0</v>
       </c>
       <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3">
         <v>100</v>
       </c>
-      <c r="AM14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1574,10 +1619,10 @@
         <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -1672,8 +1717,14 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,240 +1762,254 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F17" s="3">
         <v>3700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>3600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>4800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>2700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>2500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>2600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>4100</v>
-      </c>
-      <c r="K17" s="3">
-        <v>3200</v>
-      </c>
-      <c r="L17" s="3">
-        <v>3100</v>
       </c>
       <c r="M17" s="3">
         <v>3200</v>
       </c>
       <c r="N17" s="3">
+        <v>3100</v>
+      </c>
+      <c r="O17" s="3">
+        <v>3200</v>
+      </c>
+      <c r="P17" s="3">
         <v>5800</v>
-      </c>
-      <c r="O17" s="3">
-        <v>4700</v>
-      </c>
-      <c r="P17" s="3">
-        <v>4600</v>
       </c>
       <c r="Q17" s="3">
         <v>4700</v>
       </c>
       <c r="R17" s="3">
+        <v>4600</v>
+      </c>
+      <c r="S17" s="3">
+        <v>4700</v>
+      </c>
+      <c r="T17" s="3">
         <v>4800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>20200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>3700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>3600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>15100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>5600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>1200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>4100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>1800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>3100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>2700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>2800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>3200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>1500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>2100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>2300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>1800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>2600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>2600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>1900</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-3700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-3300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-4800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-2700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-2300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-2500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-4100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-3200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-3100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-3100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-5800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-4700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-4600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-4800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-20200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-3700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-3600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-15100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-5600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-3200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-1500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>-2300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>-1600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,53 +2050,55 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-600</v>
+        <v>-1200</v>
       </c>
       <c r="E20" s="3">
         <v>-600</v>
       </c>
       <c r="F20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="H20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-2600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>1700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-1700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-7800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>2700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>1400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -2054,44 +2121,44 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>1100</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-100</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
         <v>400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>-100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>200</v>
       </c>
-      <c r="AJ20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK20" s="3">
-        <v>0</v>
-      </c>
       <c r="AL20" s="3">
         <v>0</v>
       </c>
@@ -2101,124 +2168,136 @@
       <c r="AN20" s="3">
         <v>0</v>
       </c>
+      <c r="AO20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-3000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-2700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-5400</v>
       </c>
-      <c r="G21" s="3">
-        <v>0</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
         <v>-1200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-4200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-2300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-2600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>4700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-5800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-7200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-4300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-4600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-4800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-20200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-3700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-3500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-15000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-5500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-3100</v>
-      </c>
-      <c r="AC21" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="AD21" s="3">
-        <v>-2800</v>
       </c>
       <c r="AE21" s="3">
         <v>-2800</v>
       </c>
       <c r="AF21" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="AG21" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="AH21" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>-2100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>-2000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>-1400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>-2500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>-2500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>-1800</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2258,199 +2337,211 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
       <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
         <v>200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>200</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3">
         <v>1400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>1400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>1900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>1300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>1100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>1300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AL22" s="3">
         <v>300</v>
-      </c>
-      <c r="AK22" s="3">
-        <v>200</v>
-      </c>
-      <c r="AL22" s="3">
-        <v>200</v>
       </c>
       <c r="AM22" s="3">
         <v>200</v>
       </c>
       <c r="AN22" s="3">
+        <v>200</v>
+      </c>
+      <c r="AO22" s="3">
+        <v>200</v>
+      </c>
+      <c r="AP22" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-3000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-2700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-5300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-1100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-4000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-2200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-2300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>4800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-5700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-7200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-4300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-4700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-4800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-20400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-4200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-4100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-15700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-5800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-7600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>-2500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>-2100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>-2700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>-2100</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AP23" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2487,11 +2578,11 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -2565,8 +2656,14 @@
       <c r="AN24" s="3">
         <v>0</v>
       </c>
+      <c r="AO24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,240 +2778,258 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-3000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-2700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-5300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-1100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-4000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-2200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-2300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>4800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-5700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-7200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-4300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-4700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-4800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-20400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-4200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-4100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-15700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-5800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-7600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>-2500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>-2100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>-2700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>-2100</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-3000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-2700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-5300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-1600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-1100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-4000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-2200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-2300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>4800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-5700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-7200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-4300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-4700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-4800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-20400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-4200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-4100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-15700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-5800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-7600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>-2500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>-2100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>-2700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>-2100</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3144,14 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3145,8 +3266,14 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3388,14 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,53 +3510,59 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="E32" s="3">
         <v>600</v>
       </c>
       <c r="F32" s="3">
+        <v>600</v>
+      </c>
+      <c r="G32" s="3">
+        <v>600</v>
+      </c>
+      <c r="H32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>2600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-1700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>1700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>7800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-2700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-1400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -3446,44 +3585,44 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>2100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>2100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>100</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK32" s="3">
-        <v>0</v>
-      </c>
       <c r="AL32" s="3">
         <v>0</v>
       </c>
@@ -3493,124 +3632,136 @@
       <c r="AN32" s="3">
         <v>0</v>
       </c>
+      <c r="AO32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-3000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-2700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-5300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-1100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-4000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-2200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-2300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>4800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-5700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-7200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-4300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-4700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-4800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-20400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-4200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-4100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-15700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-5800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-7600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>-2100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>-2700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>-2100</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,245 +3876,263 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-3000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-2700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-5300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-1100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-4000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-2200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-2300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>4800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-5700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-7200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-4300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-4700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-4800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-20400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-4200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-4100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-15700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-5800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-7600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>-2100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>-2700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>-2100</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4173,10 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,113 +4217,115 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F41" s="3">
         <v>600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>6600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>17900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>19300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>21000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>2500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>3100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>300</v>
       </c>
-      <c r="Z41" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA41" s="3">
-        <v>0</v>
-      </c>
       <c r="AB41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="3">
         <v>100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>1300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>100</v>
       </c>
-      <c r="AG41" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH41" s="3">
-        <v>0</v>
-      </c>
       <c r="AI41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK41" s="3">
         <v>500</v>
       </c>
-      <c r="AJ41" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK41" s="3">
-        <v>0</v>
-      </c>
       <c r="AL41" s="3">
         <v>0</v>
       </c>
@@ -4162,56 +4335,62 @@
       <c r="AN41" s="3">
         <v>0</v>
       </c>
+      <c r="AO41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP41" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>500</v>
+      </c>
+      <c r="E42" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F42" s="3">
         <v>3900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>5800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>7900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>10200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>11600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>12400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>15300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>10200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>9800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>9800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>10500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>13100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>9900</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>4</v>
       </c>
@@ -4224,11 +4403,11 @@
       <c r="V42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
-      </c>
-      <c r="X42" s="3">
-        <v>0</v>
+      <c r="W42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y42" s="3">
         <v>0</v>
@@ -4278,8 +4457,14 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4293,17 +4478,17 @@
         <v>0</v>
       </c>
       <c r="G43" s="3">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3">
         <v>200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>200</v>
       </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
-      </c>
       <c r="K43" s="3">
         <v>0</v>
       </c>
@@ -4394,8 +4579,14 @@
       <c r="AN43" s="3">
         <v>0</v>
       </c>
+      <c r="AO43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4432,11 +4623,11 @@
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4510,31 +4701,37 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E45" s="3">
         <v>0</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>4</v>
+      <c r="F45" s="3">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3">
+        <v>0</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>4</v>
@@ -4548,38 +4745,38 @@
       <c r="N45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O45" s="3">
-        <v>400</v>
-      </c>
-      <c r="P45" s="3">
-        <v>400</v>
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q45" s="3">
         <v>400</v>
       </c>
       <c r="R45" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="S45" s="3">
         <v>400</v>
       </c>
       <c r="T45" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="U45" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="V45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W45" s="3">
         <v>100</v>
       </c>
       <c r="X45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z45" s="3">
         <v>0</v>
@@ -4588,7 +4785,7 @@
         <v>0</v>
       </c>
       <c r="AB45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC45" s="3">
         <v>0</v>
@@ -4606,7 +4803,7 @@
         <v>0</v>
       </c>
       <c r="AH45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AI45" s="3">
         <v>0</v>
@@ -4626,124 +4823,136 @@
       <c r="AN45" s="3">
         <v>0</v>
       </c>
+      <c r="AO45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F46" s="3">
         <v>4700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>7600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>9400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>11100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>13500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>15000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>16800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>11400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>12600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>12000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>12800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>15100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>16900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>18300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>19900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>21500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>1800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>2600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>3200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>1400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>100</v>
       </c>
-      <c r="AH46" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK46" s="3">
         <v>500</v>
       </c>
-      <c r="AJ46" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK46" s="3">
-        <v>0</v>
-      </c>
       <c r="AL46" s="3">
         <v>0</v>
       </c>
       <c r="AM46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO46" s="3">
         <v>100</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AP46" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4780,11 +4989,11 @@
       <c r="N47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4858,8 +5067,14 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4867,13 +5082,13 @@
         <v>300</v>
       </c>
       <c r="E48" s="3">
+        <v>400</v>
+      </c>
+      <c r="F48" s="3">
         <v>300</v>
       </c>
-      <c r="F48" s="3">
-        <v>400</v>
-      </c>
       <c r="G48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H48" s="3">
         <v>400</v>
@@ -4882,10 +5097,10 @@
         <v>400</v>
       </c>
       <c r="J48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="L48" s="3">
         <v>500</v>
@@ -4903,87 +5118,93 @@
         <v>500</v>
       </c>
       <c r="Q48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="R48" s="3">
         <v>500</v>
       </c>
       <c r="S48" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="T48" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="U48" s="3">
         <v>400</v>
       </c>
       <c r="V48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="W48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="X48" s="3">
         <v>500</v>
       </c>
       <c r="Y48" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z48" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA48" s="3">
         <v>600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>700</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>100</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>100</v>
       </c>
       <c r="AD48" s="3">
         <v>100</v>
       </c>
       <c r="AE48" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF48" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG48" s="3">
         <v>200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>200</v>
-      </c>
-      <c r="AG48" s="3">
-        <v>300</v>
-      </c>
-      <c r="AH48" s="3">
-        <v>300</v>
       </c>
       <c r="AI48" s="3">
         <v>300</v>
       </c>
       <c r="AJ48" s="3">
+        <v>300</v>
+      </c>
+      <c r="AK48" s="3">
+        <v>300</v>
+      </c>
+      <c r="AL48" s="3">
         <v>400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>500</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>500</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AP48" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E49" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="F49" s="3">
         <v>600</v>
@@ -4995,10 +5216,10 @@
         <v>600</v>
       </c>
       <c r="I49" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="J49" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="K49" s="3">
         <v>700</v>
@@ -5007,22 +5228,22 @@
         <v>700</v>
       </c>
       <c r="M49" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="N49" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="O49" s="3">
         <v>800</v>
       </c>
       <c r="P49" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>800</v>
+      </c>
+      <c r="R49" s="3">
         <v>500</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>600</v>
-      </c>
-      <c r="R49" s="3">
-        <v>600</v>
       </c>
       <c r="S49" s="3">
         <v>600</v>
@@ -5037,10 +5258,10 @@
         <v>600</v>
       </c>
       <c r="W49" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="X49" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="Y49" s="3">
         <v>700</v>
@@ -5052,10 +5273,10 @@
         <v>700</v>
       </c>
       <c r="AB49" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="AC49" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="AD49" s="3">
         <v>800</v>
@@ -5067,10 +5288,10 @@
         <v>800</v>
       </c>
       <c r="AG49" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="AH49" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="AI49" s="3">
         <v>900</v>
@@ -5085,13 +5306,19 @@
         <v>900</v>
       </c>
       <c r="AM49" s="3">
+        <v>900</v>
+      </c>
+      <c r="AN49" s="3">
+        <v>900</v>
+      </c>
+      <c r="AO49" s="3">
         <v>1000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AP49" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5433,14 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,8 +5555,14 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5366,11 +5605,11 @@
       <c r="P52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S52" s="3">
         <v>0</v>
@@ -5400,17 +5639,17 @@
         <v>0</v>
       </c>
       <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="3">
         <v>400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>200</v>
       </c>
-      <c r="AD52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE52" s="3">
-        <v>0</v>
-      </c>
       <c r="AF52" s="3">
         <v>0</v>
       </c>
@@ -5424,22 +5663,28 @@
         <v>0</v>
       </c>
       <c r="AJ52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL52" s="3">
         <v>100</v>
       </c>
-      <c r="AK52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL52" s="3">
-        <v>0</v>
-      </c>
       <c r="AM52" s="3">
         <v>0</v>
       </c>
       <c r="AN52" s="3">
         <v>0</v>
       </c>
+      <c r="AO52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,124 +5799,136 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F54" s="3">
         <v>5600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>8500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>10300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>12300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>14600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>16100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>18000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>12600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>13800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>13300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>14100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>16400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>17900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>19400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>20900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>22500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>2200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>2900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>3700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>4300</v>
-      </c>
-      <c r="X54" s="3">
-        <v>1400</v>
-      </c>
-      <c r="Y54" s="3">
-        <v>1600</v>
       </c>
       <c r="Z54" s="3">
         <v>1400</v>
       </c>
       <c r="AA54" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AB54" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AC54" s="3">
         <v>1500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>1500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>2400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>1600</v>
-      </c>
-      <c r="AE54" s="3">
-        <v>1200</v>
-      </c>
-      <c r="AF54" s="3">
-        <v>1300</v>
       </c>
       <c r="AG54" s="3">
         <v>1200</v>
       </c>
       <c r="AH54" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AI54" s="3">
         <v>1200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AK54" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>1400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>1400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>1500</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>1600</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AP54" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5969,10 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,31 +6013,33 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F57" s="3">
         <v>900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>400</v>
-      </c>
-      <c r="I57" s="3">
-        <v>200</v>
-      </c>
-      <c r="J57" s="3">
-        <v>200</v>
       </c>
       <c r="K57" s="3">
         <v>200</v>
@@ -5787,91 +6048,97 @@
         <v>200</v>
       </c>
       <c r="M57" s="3">
+        <v>200</v>
+      </c>
+      <c r="N57" s="3">
+        <v>200</v>
+      </c>
+      <c r="O57" s="3">
         <v>300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>200</v>
-      </c>
-      <c r="S57" s="3">
-        <v>100</v>
-      </c>
-      <c r="T57" s="3">
-        <v>100</v>
       </c>
       <c r="U57" s="3">
         <v>100</v>
       </c>
       <c r="V57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W57" s="3">
         <v>100</v>
       </c>
       <c r="X57" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y57" s="3">
         <v>100</v>
       </c>
-      <c r="Y57" s="3">
-        <v>0</v>
-      </c>
       <c r="Z57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="3">
         <v>2000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>2000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>1700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>1500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>1600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>1900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>2100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>2300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>2400</v>
-      </c>
-      <c r="AI57" s="3">
-        <v>2500</v>
-      </c>
-      <c r="AJ57" s="3">
-        <v>2700</v>
       </c>
       <c r="AK57" s="3">
         <v>2500</v>
       </c>
       <c r="AL57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AM57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="AN57" s="3">
         <v>2300</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>2300</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AP57" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5891,29 +6158,29 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>100</v>
-      </c>
-      <c r="K58" s="3">
-        <v>200</v>
-      </c>
-      <c r="L58" s="3">
-        <v>200</v>
       </c>
       <c r="M58" s="3">
         <v>200</v>
       </c>
       <c r="N58" s="3">
+        <v>200</v>
+      </c>
+      <c r="O58" s="3">
+        <v>200</v>
+      </c>
+      <c r="P58" s="3">
         <v>100</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -5921,14 +6188,14 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>100</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
       <c r="V58" s="3">
         <v>0</v>
       </c>
@@ -5936,290 +6203,308 @@
         <v>0</v>
       </c>
       <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
         <v>1100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>8000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>7100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>7500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>5500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>3500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>3600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>3200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>4400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>3700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>3500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>2900</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>2400</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AN58" s="3">
         <v>1900</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AO58" s="3">
         <v>1900</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AP58" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F59" s="3">
         <v>2000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>3300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>3500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>4600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1500</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q59" s="3">
         <v>300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>1000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>8300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>4600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>4400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>4100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>3600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>3700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>3700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>3900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>2700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>2500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>2100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>1800</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>1700</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AP59" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3400</v>
+        <v>1600</v>
       </c>
       <c r="E60" s="3">
         <v>3700</v>
       </c>
       <c r="F60" s="3">
-        <v>4200</v>
+        <v>3400</v>
       </c>
       <c r="G60" s="3">
         <v>3700</v>
       </c>
       <c r="H60" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I60" s="3">
+        <v>3700</v>
+      </c>
+      <c r="J60" s="3">
         <v>4600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>5300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>3400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>1300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>1000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>1400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>18400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>13700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>13700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>11100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>8700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>9300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>8900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>10600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>8800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>8400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>8000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>7000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>6100</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>5800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AP60" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -6251,17 +6536,17 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>100</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -6269,26 +6554,26 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>5800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>5000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>4700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>4300</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -6296,46 +6581,52 @@
         <v>0</v>
       </c>
       <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>1200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>400</v>
-      </c>
-      <c r="AH61" s="3">
-        <v>100</v>
-      </c>
-      <c r="AI61" s="3">
-        <v>200</v>
       </c>
       <c r="AJ61" s="3">
         <v>100</v>
       </c>
       <c r="AK61" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AL61" s="3">
         <v>100</v>
       </c>
       <c r="AM61" s="3">
+        <v>100</v>
+      </c>
+      <c r="AN61" s="3">
+        <v>100</v>
+      </c>
+      <c r="AO61" s="3">
         <v>300</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AP61" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6372,66 +6663,66 @@
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O62" s="3">
-        <v>200</v>
-      </c>
-      <c r="P62" s="3">
-        <v>200</v>
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q62" s="3">
         <v>200</v>
       </c>
       <c r="R62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="S62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="T62" s="3">
         <v>300</v>
       </c>
       <c r="U62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="V62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="W62" s="3">
         <v>400</v>
       </c>
       <c r="X62" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y62" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z62" s="3">
         <v>15100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>15200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>500</v>
       </c>
-      <c r="AB62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC62" s="3">
-        <v>0</v>
-      </c>
       <c r="AD62" s="3">
         <v>0</v>
       </c>
       <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="3">
         <v>100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>100</v>
       </c>
-      <c r="AG62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH62" s="3">
-        <v>0</v>
-      </c>
       <c r="AI62" s="3">
         <v>0</v>
       </c>
@@ -6445,13 +6736,19 @@
         <v>0</v>
       </c>
       <c r="AM62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO62" s="3">
         <v>400</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AP62" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6863,14 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6985,14 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,124 +7107,136 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3400</v>
+        <v>1600</v>
       </c>
       <c r="E66" s="3">
         <v>3700</v>
       </c>
       <c r="F66" s="3">
-        <v>4200</v>
+        <v>3400</v>
       </c>
       <c r="G66" s="3">
         <v>3700</v>
       </c>
       <c r="H66" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I66" s="3">
+        <v>3700</v>
+      </c>
+      <c r="J66" s="3">
         <v>4600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>5300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>3400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>2600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>900</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>900</v>
-      </c>
-      <c r="R66" s="3">
-        <v>800</v>
       </c>
       <c r="S66" s="3">
         <v>900</v>
       </c>
       <c r="T66" s="3">
+        <v>800</v>
+      </c>
+      <c r="U66" s="3">
+        <v>900</v>
+      </c>
+      <c r="V66" s="3">
         <v>7100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>6700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>6400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>5700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>16500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>16100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>18900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>14200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>13900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>11400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>9200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>9800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>10200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>11100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>8900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>8600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>8100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>7100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>6200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>6600</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7277,10 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7395,14 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7517,14 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7304,8 +7639,14 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,124 +7761,136 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-172100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-169900</v>
+      </c>
+      <c r="F72" s="3">
         <v>-166700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-163700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-161000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-155700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-154000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-153000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-148900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-146700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-164200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-161300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-158300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-152600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-148300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-143600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-139000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-134100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-113700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-109600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-105500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-89800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-84100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-83200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-86100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-78600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-77000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-72000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-67800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-63900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-60400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>-57400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>-53900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>-51400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>-49500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>-47500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>-44700</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>-42000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AP72" s="3">
         <v>-39900</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +8005,14 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +8127,14 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,124 +8249,136 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>300</v>
+      </c>
+      <c r="F76" s="3">
         <v>2200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>4800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>6100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>8500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>10000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>10800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>14500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>10000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>12800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>12400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>13500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>15800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>17000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>18600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>20100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>21600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>-4900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>-3800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>-2700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>-1300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>-15100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>-14400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>-17500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>-12800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>-12400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>-8900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>-7700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>-8600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>-8900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>-9900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>-7700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>-6800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>-6700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>-5700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>-4700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>-5000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,245 +8493,263 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-3000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-2700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-5300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-1100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-4000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-2200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-2300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>4800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-5700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-7200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-4300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-4700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-4800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-20400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-4200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-4100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-15700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-5800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-7600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>-2100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>-2700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>-2100</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,16 +8790,18 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
@@ -8464,7 +8861,7 @@
         <v>0</v>
       </c>
       <c r="Y83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z83" s="3">
         <v>0</v>
@@ -8473,7 +8870,7 @@
         <v>100</v>
       </c>
       <c r="AB83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC83" s="3">
         <v>100</v>
@@ -8511,8 +8908,14 @@
       <c r="AN83" s="3">
         <v>100</v>
       </c>
+      <c r="AO83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AP83" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +9030,14 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +9152,14 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9274,14 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9396,14 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,124 +9518,136 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F89" s="3">
         <v>-2900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-2700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-2800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-2300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-2300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-1200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-1300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-2400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-1600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-1300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-1600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-1100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>-500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>-800</v>
-      </c>
-      <c r="AL89" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="AM89" s="3">
-        <v>-1100</v>
       </c>
       <c r="AN89" s="3">
         <v>-1200</v>
       </c>
+      <c r="AO89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AP89" s="3">
+        <v>-1200</v>
+      </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,16 +9688,18 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -9267,25 +9708,25 @@
         <v>0</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
@@ -9294,31 +9735,31 @@
         <v>-100</v>
       </c>
       <c r="Q91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R91" s="3">
         <v>-100</v>
       </c>
       <c r="S91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>4</v>
+        <v>-100</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="X91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
@@ -9329,23 +9770,23 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH91" s="3" t="s">
-        <v>4</v>
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
       </c>
       <c r="AI91" s="3" t="s">
         <v>4</v>
@@ -9359,14 +9800,20 @@
       <c r="AL91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AM91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN91" s="3">
+      <c r="AM91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP91" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9928,14 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,62 +10050,68 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F94" s="3">
         <v>2000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>2100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>2400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>1500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>3000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-4900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>2500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-3200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>4</v>
       </c>
@@ -9662,11 +10121,11 @@
       <c r="W94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>0</v>
+      <c r="X94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z94" s="3">
         <v>0</v>
@@ -9677,29 +10136,29 @@
       <c r="AB94" s="3">
         <v>0</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ94" s="3">
-        <v>0</v>
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AK94" s="3">
         <v>0</v>
@@ -9713,8 +10172,14 @@
       <c r="AN94" s="3">
         <v>0</v>
       </c>
+      <c r="AO94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,8 +10220,10 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9793,11 +10260,11 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -9871,8 +10338,14 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10460,14 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10582,14 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,49 +10704,55 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="E100" s="3">
         <v>900</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
+        <v>900</v>
+      </c>
+      <c r="H100" s="3">
         <v>1100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>7500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>1900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>400</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
+      <c r="P100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q100" s="3">
         <v>0</v>
@@ -10270,73 +10761,79 @@
         <v>0</v>
       </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>21100</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>3500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>1200</v>
-      </c>
-      <c r="Z100" s="3">
-        <v>500</v>
-      </c>
-      <c r="AA100" s="3">
-        <v>1700</v>
       </c>
       <c r="AB100" s="3">
         <v>500</v>
       </c>
       <c r="AC100" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AD100" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE100" s="3">
         <v>2200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>2400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>1600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>1500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>1000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>800</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>1200</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>1100</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10373,11 +10870,11 @@
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -10451,113 +10948,119 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>900</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>1100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-1600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-4900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-11400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-1400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-1700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>19900</v>
-      </c>
-      <c r="T102" s="3">
-        <v>-600</v>
-      </c>
-      <c r="U102" s="3">
-        <v>-700</v>
       </c>
       <c r="V102" s="3">
         <v>-600</v>
       </c>
       <c r="W102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="X102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Y102" s="3">
         <v>2900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>300</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
         <v>-100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>400</v>
       </c>
-      <c r="AE102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>100</v>
       </c>
-      <c r="AG102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>-400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>500</v>
       </c>
-      <c r="AJ102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK102" s="3">
-        <v>0</v>
-      </c>
       <c r="AL102" s="3">
         <v>0</v>
       </c>
@@ -10565,6 +11068,12 @@
         <v>0</v>
       </c>
       <c r="AN102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP102" s="3">
         <v>-500</v>
       </c>
     </row>
